--- a/BA LAB.xlsx
+++ b/BA LAB.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sruthi K\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D2A253DB-DA6E-4605-8CE5-78CFCDACDD93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18498459-417B-48FA-B930-CD8F42882BE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="7" xr2:uid="{33E82029-DB00-4982-9032-79539837CD15}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="3" activeTab="10" xr2:uid="{33E82029-DB00-4982-9032-79539837CD15}"/>
   </bookViews>
   <sheets>
     <sheet name="EX 1" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,9 @@
     <sheet name="EX 4B" sheetId="6" r:id="rId6"/>
     <sheet name="EX 4C" sheetId="7" r:id="rId7"/>
     <sheet name="EX 5" sheetId="8" r:id="rId8"/>
+    <sheet name="EX 6" sheetId="9" r:id="rId9"/>
+    <sheet name="EX 7A" sheetId="10" r:id="rId10"/>
+    <sheet name="EX 7B" sheetId="11" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="ExternalData_1" localSheetId="2" hidden="1">'EX 2B'!$A$1:$L$101</definedName>
@@ -52,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1154" uniqueCount="1072">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1285" uniqueCount="1104">
   <si>
     <t>VALUES</t>
   </si>
@@ -3268,6 +3271,102 @@
   </si>
   <si>
     <t>Total</t>
+  </si>
+  <si>
+    <t>M1</t>
+  </si>
+  <si>
+    <t>M2</t>
+  </si>
+  <si>
+    <t>ANANYA</t>
+  </si>
+  <si>
+    <t>RAJU</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Region</t>
+  </si>
+  <si>
+    <t>Quantity (X)</t>
+  </si>
+  <si>
+    <t>Discount (Y)</t>
+  </si>
+  <si>
+    <t>Furniture</t>
+  </si>
+  <si>
+    <t>South</t>
+  </si>
+  <si>
+    <t>Office Supplies</t>
+  </si>
+  <si>
+    <t>Technology</t>
+  </si>
+  <si>
+    <t>Central</t>
+  </si>
+  <si>
+    <t>SUMMARY OUTPUT</t>
+  </si>
+  <si>
+    <t>Regression Statistics</t>
+  </si>
+  <si>
+    <t>Multiple R</t>
+  </si>
+  <si>
+    <t>R Square</t>
+  </si>
+  <si>
+    <t>Adjusted R Square</t>
+  </si>
+  <si>
+    <t>Regression</t>
+  </si>
+  <si>
+    <t>Residual</t>
+  </si>
+  <si>
+    <t>Intercept</t>
+  </si>
+  <si>
+    <t>Significance F</t>
+  </si>
+  <si>
+    <t>Coefficients</t>
+  </si>
+  <si>
+    <t>Lower 95%</t>
+  </si>
+  <si>
+    <t>Upper 95%</t>
+  </si>
+  <si>
+    <t>Lower 95.0%</t>
+  </si>
+  <si>
+    <t>Upper 95.0%</t>
+  </si>
+  <si>
+    <t>X Variable 1</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>Discount</t>
+  </si>
+  <si>
+    <t>Profit</t>
+  </si>
+  <si>
+    <t>X Variable 2</t>
   </si>
 </sst>
 </file>
@@ -3316,7 +3415,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -3339,11 +3438,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3364,20 +3483,38 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3428,6 +3565,946 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'EX 6'!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>M1</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>'EX 6'!$B$2:$B$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>89</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>87</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1BE8-431F-BCCC-C69FE9BAD16E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'EX 6'!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>M2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>'EX 6'!$C$2:$C$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>89</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>90</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-1BE8-431F-BCCC-C69FE9BAD16E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1397022592"/>
+        <c:axId val="1275932048"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1397022592"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1275932048"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:tickLblSkip val="1"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1275932048"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1397022592"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>454025</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>88900</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>149225</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>69850</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CB8D89C1-CFA1-5B23-9BCE-BD34AD2CFE48}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3784,10 +4861,10 @@
       <c r="C1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="8"/>
+      <c r="F1" s="14"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="6">
@@ -3908,6 +4985,1095 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{307A826A-2EAD-4609-8E68-25A9F115B5DA}">
+  <dimension ref="A1:N23"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="16.7265625" style="18" customWidth="1"/>
+    <col min="2" max="2" width="10.7265625" style="18" customWidth="1"/>
+    <col min="3" max="5" width="8.7265625" style="18"/>
+    <col min="6" max="6" width="16.36328125" style="18" customWidth="1"/>
+    <col min="7" max="7" width="13" style="18" customWidth="1"/>
+    <col min="8" max="8" width="12.7265625" style="18" customWidth="1"/>
+    <col min="9" max="9" width="8.7265625" style="18"/>
+    <col min="10" max="10" width="11.1796875" style="18" customWidth="1"/>
+    <col min="11" max="11" width="11.6328125" style="18" customWidth="1"/>
+    <col min="12" max="12" width="10.36328125" style="18" customWidth="1"/>
+    <col min="13" max="13" width="11.1796875" style="18" customWidth="1"/>
+    <col min="14" max="14" width="12.6328125" style="18" customWidth="1"/>
+    <col min="15" max="16384" width="8.7265625" style="18"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A1" s="16" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A2" s="19" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C2" s="20">
+        <v>2</v>
+      </c>
+      <c r="D2" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A3" s="19" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C3" s="20">
+        <v>3</v>
+      </c>
+      <c r="D3" s="20">
+        <v>2</v>
+      </c>
+      <c r="F3" t="s">
+        <v>1085</v>
+      </c>
+      <c r="G3"/>
+      <c r="H3"/>
+      <c r="I3"/>
+      <c r="J3"/>
+      <c r="K3"/>
+      <c r="L3"/>
+      <c r="M3"/>
+      <c r="N3"/>
+    </row>
+    <row r="4" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="19" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>584</v>
+      </c>
+      <c r="C4" s="20">
+        <v>2</v>
+      </c>
+      <c r="D4" s="20">
+        <v>0.3</v>
+      </c>
+      <c r="F4"/>
+      <c r="G4"/>
+      <c r="H4"/>
+      <c r="I4"/>
+      <c r="J4"/>
+      <c r="K4"/>
+      <c r="L4"/>
+      <c r="M4"/>
+      <c r="N4"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A5" s="19" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C5" s="20">
+        <v>5</v>
+      </c>
+      <c r="D5" s="20">
+        <v>0.45</v>
+      </c>
+      <c r="F5" s="24" t="s">
+        <v>1086</v>
+      </c>
+      <c r="G5" s="24"/>
+      <c r="H5"/>
+      <c r="I5"/>
+      <c r="J5"/>
+      <c r="K5"/>
+      <c r="L5"/>
+      <c r="M5"/>
+      <c r="N5"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A6" s="19" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C6" s="20">
+        <v>2</v>
+      </c>
+      <c r="D6" s="20">
+        <v>0.2</v>
+      </c>
+      <c r="F6" s="21" t="s">
+        <v>1087</v>
+      </c>
+      <c r="G6" s="21">
+        <v>0.15864455651225881</v>
+      </c>
+      <c r="H6"/>
+      <c r="I6"/>
+      <c r="J6"/>
+      <c r="K6"/>
+      <c r="L6"/>
+      <c r="M6"/>
+      <c r="N6"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A7" s="19" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>584</v>
+      </c>
+      <c r="C7" s="20">
+        <v>7</v>
+      </c>
+      <c r="D7" s="20">
+        <v>0.6</v>
+      </c>
+      <c r="F7" s="21" t="s">
+        <v>1088</v>
+      </c>
+      <c r="G7" s="21">
+        <v>2.5168095310971281E-2</v>
+      </c>
+      <c r="H7"/>
+      <c r="I7"/>
+      <c r="J7"/>
+      <c r="K7"/>
+      <c r="L7"/>
+      <c r="M7"/>
+      <c r="N7"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A8" s="19" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>584</v>
+      </c>
+      <c r="C8" s="20">
+        <v>4</v>
+      </c>
+      <c r="D8" s="20">
+        <v>1</v>
+      </c>
+      <c r="F8" s="21" t="s">
+        <v>1089</v>
+      </c>
+      <c r="G8" s="21">
+        <v>-4.4462755023959341E-2</v>
+      </c>
+      <c r="H8"/>
+      <c r="I8"/>
+      <c r="J8"/>
+      <c r="K8"/>
+      <c r="L8"/>
+      <c r="M8"/>
+      <c r="N8"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A9" s="19" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>584</v>
+      </c>
+      <c r="C9" s="20">
+        <v>6</v>
+      </c>
+      <c r="D9" s="20">
+        <v>0.2</v>
+      </c>
+      <c r="F9" s="21" t="s">
+        <v>1024</v>
+      </c>
+      <c r="G9" s="21">
+        <v>0.50204860162347231</v>
+      </c>
+      <c r="H9"/>
+      <c r="I9"/>
+      <c r="J9"/>
+      <c r="K9"/>
+      <c r="L9"/>
+      <c r="M9"/>
+      <c r="N9"/>
+    </row>
+    <row r="10" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="19" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>584</v>
+      </c>
+      <c r="C10" s="20">
+        <v>3</v>
+      </c>
+      <c r="D10" s="20">
+        <v>0.2</v>
+      </c>
+      <c r="F10" s="22" t="s">
+        <v>1039</v>
+      </c>
+      <c r="G10" s="22">
+        <v>16</v>
+      </c>
+      <c r="H10"/>
+      <c r="I10"/>
+      <c r="J10"/>
+      <c r="K10"/>
+      <c r="L10"/>
+      <c r="M10"/>
+      <c r="N10"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A11" s="19" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>584</v>
+      </c>
+      <c r="C11" s="20">
+        <v>5</v>
+      </c>
+      <c r="D11" s="20">
+        <v>0.8</v>
+      </c>
+      <c r="F11"/>
+      <c r="G11"/>
+      <c r="H11"/>
+      <c r="I11"/>
+      <c r="J11"/>
+      <c r="K11"/>
+      <c r="L11"/>
+      <c r="M11"/>
+      <c r="N11"/>
+    </row>
+    <row r="12" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="19" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>584</v>
+      </c>
+      <c r="C12" s="20">
+        <v>9</v>
+      </c>
+      <c r="D12" s="20">
+        <v>0.2</v>
+      </c>
+      <c r="F12" t="s">
+        <v>1062</v>
+      </c>
+      <c r="G12"/>
+      <c r="H12"/>
+      <c r="I12"/>
+      <c r="J12"/>
+      <c r="K12"/>
+      <c r="L12"/>
+      <c r="M12"/>
+      <c r="N12"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A13" s="19" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>584</v>
+      </c>
+      <c r="C13" s="20">
+        <v>4</v>
+      </c>
+      <c r="D13" s="20">
+        <v>0.2</v>
+      </c>
+      <c r="F13" s="23"/>
+      <c r="G13" s="23" t="s">
+        <v>1050</v>
+      </c>
+      <c r="H13" s="23" t="s">
+        <v>1064</v>
+      </c>
+      <c r="I13" s="23" t="s">
+        <v>1065</v>
+      </c>
+      <c r="J13" s="23" t="s">
+        <v>1066</v>
+      </c>
+      <c r="K13" s="23" t="s">
+        <v>1093</v>
+      </c>
+      <c r="L13"/>
+      <c r="M13"/>
+      <c r="N13"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A14" s="19" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C14" s="20">
+        <v>3</v>
+      </c>
+      <c r="D14" s="20">
+        <v>0.2</v>
+      </c>
+      <c r="F14" s="21" t="s">
+        <v>1090</v>
+      </c>
+      <c r="G14" s="21">
+        <v>1</v>
+      </c>
+      <c r="H14" s="21">
+        <v>9.1104572510823711E-2</v>
+      </c>
+      <c r="I14" s="21">
+        <v>9.1104572510823711E-2</v>
+      </c>
+      <c r="J14" s="21">
+        <v>0.36145035124388819</v>
+      </c>
+      <c r="K14" s="21">
+        <v>0.55731162586537575</v>
+      </c>
+      <c r="L14"/>
+      <c r="M14"/>
+      <c r="N14"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A15" s="19" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>584</v>
+      </c>
+      <c r="C15" s="20">
+        <v>3</v>
+      </c>
+      <c r="D15" s="20">
+        <v>0.2</v>
+      </c>
+      <c r="F15" s="21" t="s">
+        <v>1091</v>
+      </c>
+      <c r="G15" s="21">
+        <v>14</v>
+      </c>
+      <c r="H15" s="21">
+        <v>3.528739177489177</v>
+      </c>
+      <c r="I15" s="21">
+        <v>0.25205279839208405</v>
+      </c>
+      <c r="J15" s="21"/>
+      <c r="K15" s="21"/>
+      <c r="L15"/>
+      <c r="M15"/>
+      <c r="N15"/>
+    </row>
+    <row r="16" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="19" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C16" s="20">
+        <v>5</v>
+      </c>
+      <c r="D16" s="20">
+        <v>0.8</v>
+      </c>
+      <c r="F16" s="22" t="s">
+        <v>1071</v>
+      </c>
+      <c r="G16" s="22">
+        <v>15</v>
+      </c>
+      <c r="H16" s="22">
+        <v>3.6198437500000007</v>
+      </c>
+      <c r="I16" s="22"/>
+      <c r="J16" s="22"/>
+      <c r="K16" s="22"/>
+      <c r="L16"/>
+      <c r="M16"/>
+      <c r="N16"/>
+    </row>
+    <row r="17" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="19" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C17" s="20">
+        <v>3</v>
+      </c>
+      <c r="D17" s="20">
+        <v>0.8</v>
+      </c>
+      <c r="F17"/>
+      <c r="G17"/>
+      <c r="H17"/>
+      <c r="I17"/>
+      <c r="J17"/>
+      <c r="K17"/>
+      <c r="L17"/>
+      <c r="M17"/>
+      <c r="N17"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="F18" s="23"/>
+      <c r="G18" s="23" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H18" s="23" t="s">
+        <v>1024</v>
+      </c>
+      <c r="I18" s="23" t="s">
+        <v>1051</v>
+      </c>
+      <c r="J18" s="23" t="s">
+        <v>1067</v>
+      </c>
+      <c r="K18" s="23" t="s">
+        <v>1095</v>
+      </c>
+      <c r="L18" s="23" t="s">
+        <v>1096</v>
+      </c>
+      <c r="M18" s="23" t="s">
+        <v>1097</v>
+      </c>
+      <c r="N18" s="23" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="F19" s="21" t="s">
+        <v>1092</v>
+      </c>
+      <c r="G19" s="21">
+        <v>0.73571428571428588</v>
+      </c>
+      <c r="H19" s="21">
+        <v>0.30003142596834992</v>
+      </c>
+      <c r="I19" s="21">
+        <v>2.4521240844680579</v>
+      </c>
+      <c r="J19" s="21">
+        <v>2.7929450079556883E-2</v>
+      </c>
+      <c r="K19" s="21">
+        <v>9.2210877340372699E-2</v>
+      </c>
+      <c r="L19" s="21">
+        <v>1.3792176940881991</v>
+      </c>
+      <c r="M19" s="21">
+        <v>9.2210877340372699E-2</v>
+      </c>
+      <c r="N19" s="21">
+        <v>1.3792176940881991</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="F20" s="22" t="s">
+        <v>1099</v>
+      </c>
+      <c r="G20" s="22">
+        <v>-3.9718614718614716E-2</v>
+      </c>
+      <c r="H20" s="22">
+        <v>6.6064745678069095E-2</v>
+      </c>
+      <c r="I20" s="22">
+        <v>-0.60120741116846133</v>
+      </c>
+      <c r="J20" s="22">
+        <v>0.5573116258653783</v>
+      </c>
+      <c r="K20" s="22">
+        <v>-0.1814134017896126</v>
+      </c>
+      <c r="L20" s="22">
+        <v>0.10197617235238318</v>
+      </c>
+      <c r="M20" s="22">
+        <v>-0.1814134017896126</v>
+      </c>
+      <c r="N20" s="22">
+        <v>0.10197617235238318</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="F21"/>
+      <c r="G21"/>
+      <c r="H21"/>
+      <c r="I21"/>
+      <c r="J21"/>
+      <c r="K21"/>
+      <c r="L21"/>
+      <c r="M21"/>
+      <c r="N21"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="F22"/>
+      <c r="G22"/>
+      <c r="H22"/>
+      <c r="I22"/>
+      <c r="J22"/>
+      <c r="K22"/>
+      <c r="L22"/>
+      <c r="M22"/>
+      <c r="N22"/>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="F23"/>
+      <c r="G23"/>
+      <c r="H23"/>
+      <c r="I23"/>
+      <c r="J23"/>
+      <c r="K23"/>
+      <c r="L23"/>
+      <c r="M23"/>
+      <c r="N23"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F40E832E-7A5F-46A7-A3B9-2EE9E93AF6A6}">
+  <dimension ref="A1:O20"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.08984375" customWidth="1"/>
+    <col min="8" max="8" width="13.36328125" customWidth="1"/>
+    <col min="9" max="9" width="13" customWidth="1"/>
+    <col min="10" max="10" width="12.90625" customWidth="1"/>
+    <col min="11" max="11" width="10.54296875" customWidth="1"/>
+    <col min="12" max="12" width="13.08984375" customWidth="1"/>
+    <col min="13" max="13" width="10.54296875" customWidth="1"/>
+    <col min="14" max="14" width="11.1796875" customWidth="1"/>
+    <col min="15" max="15" width="11.81640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="8" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>1100</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>1101</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="6" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C2" s="6">
+        <v>2</v>
+      </c>
+      <c r="D2" s="6">
+        <v>1</v>
+      </c>
+      <c r="E2" s="6">
+        <v>261.95999999999998</v>
+      </c>
+      <c r="G2" s="18" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="6" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C3" s="6">
+        <v>3</v>
+      </c>
+      <c r="D3" s="6">
+        <v>2</v>
+      </c>
+      <c r="E3" s="6">
+        <v>731.94</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" s="6" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>584</v>
+      </c>
+      <c r="C4" s="6">
+        <v>2</v>
+      </c>
+      <c r="D4" s="6">
+        <v>0.3</v>
+      </c>
+      <c r="E4" s="6">
+        <v>14.67</v>
+      </c>
+      <c r="G4" s="24" t="s">
+        <v>1086</v>
+      </c>
+      <c r="H4" s="24"/>
+    </row>
+    <row r="5" spans="1:12" ht="17" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="6" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C5" s="6">
+        <v>5</v>
+      </c>
+      <c r="D5" s="6">
+        <v>0.45</v>
+      </c>
+      <c r="E5" s="6">
+        <v>957.57799999999997</v>
+      </c>
+      <c r="G5" s="21" t="s">
+        <v>1087</v>
+      </c>
+      <c r="H5" s="21">
+        <v>0.59561718864040003</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A6" s="6" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C6" s="6">
+        <v>2</v>
+      </c>
+      <c r="D6" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="E6" s="6">
+        <v>22.367999999999999</v>
+      </c>
+      <c r="G6" s="21" t="s">
+        <v>1088</v>
+      </c>
+      <c r="H6" s="21">
+        <v>0.35475983540389383</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="17" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="6" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>584</v>
+      </c>
+      <c r="C7" s="6">
+        <v>7</v>
+      </c>
+      <c r="D7" s="6">
+        <v>0.6</v>
+      </c>
+      <c r="E7" s="6">
+        <v>48.86</v>
+      </c>
+      <c r="G7" s="21" t="s">
+        <v>1089</v>
+      </c>
+      <c r="H7" s="21">
+        <v>0.24721980797120949</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A8" s="6" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>584</v>
+      </c>
+      <c r="C8" s="6">
+        <v>4</v>
+      </c>
+      <c r="D8" s="6">
+        <v>1</v>
+      </c>
+      <c r="E8" s="6">
+        <v>7.28</v>
+      </c>
+      <c r="G8" s="21" t="s">
+        <v>1024</v>
+      </c>
+      <c r="H8" s="21">
+        <v>446.96688967125851</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="6" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>584</v>
+      </c>
+      <c r="C9" s="6">
+        <v>6</v>
+      </c>
+      <c r="D9" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="E9" s="6">
+        <v>907.15200000000004</v>
+      </c>
+      <c r="G9" s="22" t="s">
+        <v>1039</v>
+      </c>
+      <c r="H9" s="22">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A10" s="6" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>584</v>
+      </c>
+      <c r="C10" s="6">
+        <v>3</v>
+      </c>
+      <c r="D10" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="E10" s="6">
+        <v>18.504000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="6" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>584</v>
+      </c>
+      <c r="C11" s="6">
+        <v>5</v>
+      </c>
+      <c r="D11" s="6">
+        <v>0.8</v>
+      </c>
+      <c r="E11" s="6">
+        <v>114.9</v>
+      </c>
+      <c r="G11" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="6" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>584</v>
+      </c>
+      <c r="C12" s="6">
+        <v>9</v>
+      </c>
+      <c r="D12" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="E12" s="6">
+        <v>1706.18</v>
+      </c>
+      <c r="G12" s="23"/>
+      <c r="H12" s="23" t="s">
+        <v>1050</v>
+      </c>
+      <c r="I12" s="23" t="s">
+        <v>1064</v>
+      </c>
+      <c r="J12" s="23" t="s">
+        <v>1065</v>
+      </c>
+      <c r="K12" s="23" t="s">
+        <v>1066</v>
+      </c>
+      <c r="L12" s="23" t="s">
+        <v>1093</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A13" s="6" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>584</v>
+      </c>
+      <c r="C13" s="6">
+        <v>4</v>
+      </c>
+      <c r="D13" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="E13" s="6">
+        <v>911.42399999999998</v>
+      </c>
+      <c r="G13" s="21" t="s">
+        <v>1090</v>
+      </c>
+      <c r="H13" s="21">
+        <v>2</v>
+      </c>
+      <c r="I13" s="21">
+        <v>1318089.8111541453</v>
+      </c>
+      <c r="J13" s="21">
+        <v>659044.90557707264</v>
+      </c>
+      <c r="K13" s="21">
+        <v>3.2988631663308707</v>
+      </c>
+      <c r="L13" s="21">
+        <v>7.2165289777997271E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A14" s="6" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C14" s="6">
+        <v>3</v>
+      </c>
+      <c r="D14" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="E14" s="6">
+        <v>15.552</v>
+      </c>
+      <c r="G14" s="21" t="s">
+        <v>1091</v>
+      </c>
+      <c r="H14" s="21">
+        <v>12</v>
+      </c>
+      <c r="I14" s="21">
+        <v>2397352.805548788</v>
+      </c>
+      <c r="J14" s="21">
+        <v>199779.400462399</v>
+      </c>
+      <c r="K14" s="21"/>
+      <c r="L14" s="21"/>
+    </row>
+    <row r="15" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="6" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>584</v>
+      </c>
+      <c r="C15" s="6">
+        <v>3</v>
+      </c>
+      <c r="D15" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="E15" s="6">
+        <v>407.976</v>
+      </c>
+      <c r="G15" s="22" t="s">
+        <v>1071</v>
+      </c>
+      <c r="H15" s="22">
+        <v>14</v>
+      </c>
+      <c r="I15" s="22">
+        <v>3715442.6167029333</v>
+      </c>
+      <c r="J15" s="22"/>
+      <c r="K15" s="22"/>
+      <c r="L15" s="22"/>
+    </row>
+    <row r="16" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="6" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C16" s="6">
+        <v>5</v>
+      </c>
+      <c r="D16" s="6">
+        <v>0.8</v>
+      </c>
+      <c r="E16" s="6">
+        <v>68.81</v>
+      </c>
+    </row>
+    <row r="17" spans="7:15" x14ac:dyDescent="0.35">
+      <c r="G17" s="23"/>
+      <c r="H17" s="23" t="s">
+        <v>1094</v>
+      </c>
+      <c r="I17" s="23" t="s">
+        <v>1024</v>
+      </c>
+      <c r="J17" s="23" t="s">
+        <v>1051</v>
+      </c>
+      <c r="K17" s="23" t="s">
+        <v>1067</v>
+      </c>
+      <c r="L17" s="23" t="s">
+        <v>1095</v>
+      </c>
+      <c r="M17" s="23" t="s">
+        <v>1096</v>
+      </c>
+      <c r="N17" s="23" t="s">
+        <v>1097</v>
+      </c>
+      <c r="O17" s="23" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="18" spans="7:15" x14ac:dyDescent="0.35">
+      <c r="G18" s="21" t="s">
+        <v>1092</v>
+      </c>
+      <c r="H18" s="21">
+        <v>-229.60883986974579</v>
+      </c>
+      <c r="I18" s="21">
+        <v>323.12080775361602</v>
+      </c>
+      <c r="J18" s="21">
+        <v>-0.71059750520562459</v>
+      </c>
+      <c r="K18" s="21">
+        <v>0.49091432814138225</v>
+      </c>
+      <c r="L18" s="21">
+        <v>-933.62860133576248</v>
+      </c>
+      <c r="M18" s="21">
+        <v>474.4109215962709</v>
+      </c>
+      <c r="N18" s="21">
+        <v>-933.62860133576248</v>
+      </c>
+      <c r="O18" s="21">
+        <v>474.4109215962709</v>
+      </c>
+    </row>
+    <row r="19" spans="7:15" x14ac:dyDescent="0.35">
+      <c r="G19" s="21" t="s">
+        <v>1099</v>
+      </c>
+      <c r="H19" s="21">
+        <v>152.90148804422148</v>
+      </c>
+      <c r="I19" s="21">
+        <v>60.129656285644458</v>
+      </c>
+      <c r="J19" s="21">
+        <v>2.5428631641908397</v>
+      </c>
+      <c r="K19" s="21">
+        <v>2.5802116328728902E-2</v>
+      </c>
+      <c r="L19" s="21">
+        <v>21.890221485578621</v>
+      </c>
+      <c r="M19" s="21">
+        <v>283.91275460286431</v>
+      </c>
+      <c r="N19" s="21">
+        <v>21.890221485578621</v>
+      </c>
+      <c r="O19" s="21">
+        <v>283.91275460286431</v>
+      </c>
+    </row>
+    <row r="20" spans="7:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="G20" s="22" t="s">
+        <v>1103</v>
+      </c>
+      <c r="H20" s="22">
+        <v>0.77758697727322768</v>
+      </c>
+      <c r="I20" s="22">
+        <v>239.18785121373512</v>
+      </c>
+      <c r="J20" s="22">
+        <v>3.250946790681213E-3</v>
+      </c>
+      <c r="K20" s="22">
+        <v>0.99745954399177317</v>
+      </c>
+      <c r="L20" s="22">
+        <v>-520.36797194774897</v>
+      </c>
+      <c r="M20" s="22">
+        <v>521.92314590229546</v>
+      </c>
+      <c r="N20" s="22">
+        <v>-520.36797194774897</v>
+      </c>
+      <c r="O20" s="22">
+        <v>521.92314590229546</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFD39369-00E3-45FB-8F11-75011437060D}">
   <dimension ref="A1:D13"/>
@@ -3915,7 +6081,7 @@
   <cols>
     <col min="1" max="1" width="8.7265625" style="1"/>
     <col min="2" max="2" width="10.26953125" customWidth="1"/>
-    <col min="3" max="3" width="10.54296875" style="11" customWidth="1"/>
+    <col min="3" max="3" width="10.54296875" customWidth="1"/>
     <col min="4" max="4" width="11.7265625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3940,7 +6106,7 @@
       <c r="B2" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="10">
+      <c r="C2" s="6">
         <v>99</v>
       </c>
       <c r="D2" s="6">
@@ -3954,7 +6120,7 @@
       <c r="B3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="10">
+      <c r="C3" s="6">
         <v>86</v>
       </c>
       <c r="D3" s="6">
@@ -3968,7 +6134,7 @@
       <c r="B4" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4" s="6">
         <v>78</v>
       </c>
       <c r="D4" s="6">
@@ -3982,7 +6148,7 @@
       <c r="B5" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="6">
         <v>55</v>
       </c>
       <c r="D5" s="6">
@@ -3996,7 +6162,7 @@
       <c r="B6" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="6">
         <v>87</v>
       </c>
       <c r="D6" s="6">
@@ -4004,10 +6170,10 @@
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="6">
         <f>MAX(C2:C6)</f>
         <v>99</v>
       </c>
@@ -4017,10 +6183,10 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="6">
         <f>MIN(C2:C6)</f>
         <v>55</v>
       </c>
@@ -4030,10 +6196,10 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="10">
+      <c r="C10" s="6">
         <f>AVERAGE(C2:C6)</f>
         <v>81</v>
       </c>
@@ -4043,10 +6209,10 @@
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="10">
+      <c r="C11" s="6">
         <f>SUM(C2:C6)</f>
         <v>405</v>
       </c>
@@ -4056,27 +6222,27 @@
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="13">
+      <c r="C12" s="11">
         <f>SQRT(C2)</f>
         <v>9.9498743710661994</v>
       </c>
-      <c r="D12" s="14">
+      <c r="D12" s="11">
         <f>SQRT(D2)</f>
         <v>9.7467943448089631</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="13">
+      <c r="C13" s="11">
         <f>ROUND(C12,0)</f>
         <v>10</v>
       </c>
-      <c r="D13" s="14">
+      <c r="D13" s="11">
         <f>ROUND(D12,0)</f>
         <v>10</v>
       </c>
@@ -4146,37 +6312,37 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" t="s">
         <v>49</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" t="s">
         <v>50</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="D2" t="s">
         <v>51</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" t="s">
         <v>52</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="F2" t="s">
         <v>53</v>
       </c>
-      <c r="G2" s="15" t="s">
+      <c r="G2" t="s">
         <v>54</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="H2" t="s">
         <v>55</v>
       </c>
-      <c r="I2" s="15" t="s">
+      <c r="I2" t="s">
         <v>56</v>
       </c>
-      <c r="J2" s="15" t="s">
+      <c r="J2" t="s">
         <v>57</v>
       </c>
-      <c r="K2" s="16">
+      <c r="K2" s="12">
         <v>44067</v>
       </c>
-      <c r="L2" s="15" t="s">
+      <c r="L2" t="s">
         <v>58</v>
       </c>
     </row>
@@ -4184,37 +6350,37 @@
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" t="s">
         <v>59</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" t="s">
         <v>60</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" t="s">
         <v>61</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="E3" t="s">
         <v>62</v>
       </c>
-      <c r="F3" s="15" t="s">
+      <c r="F3" t="s">
         <v>63</v>
       </c>
-      <c r="G3" s="15" t="s">
+      <c r="G3" t="s">
         <v>64</v>
       </c>
-      <c r="H3" s="15" t="s">
+      <c r="H3" t="s">
         <v>65</v>
       </c>
-      <c r="I3" s="15" t="s">
+      <c r="I3" t="s">
         <v>66</v>
       </c>
-      <c r="J3" s="15" t="s">
+      <c r="J3" t="s">
         <v>67</v>
       </c>
-      <c r="K3" s="16">
+      <c r="K3" s="12">
         <v>44309</v>
       </c>
-      <c r="L3" s="15" t="s">
+      <c r="L3" t="s">
         <v>68</v>
       </c>
     </row>
@@ -4222,37 +6388,37 @@
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" t="s">
         <v>69</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" t="s">
         <v>70</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" t="s">
         <v>71</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" t="s">
         <v>72</v>
       </c>
-      <c r="F4" s="15" t="s">
+      <c r="F4" t="s">
         <v>73</v>
       </c>
-      <c r="G4" s="15" t="s">
+      <c r="G4" t="s">
         <v>74</v>
       </c>
-      <c r="H4" s="15" t="s">
+      <c r="H4" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="15" t="s">
+      <c r="I4" t="s">
         <v>76</v>
       </c>
-      <c r="J4" s="15" t="s">
+      <c r="J4" t="s">
         <v>77</v>
       </c>
-      <c r="K4" s="16">
+      <c r="K4" s="12">
         <v>43915</v>
       </c>
-      <c r="L4" s="15" t="s">
+      <c r="L4" t="s">
         <v>78</v>
       </c>
     </row>
@@ -4260,37 +6426,37 @@
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" t="s">
         <v>79</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" t="s">
         <v>80</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" t="s">
         <v>81</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" t="s">
         <v>82</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="F5" t="s">
         <v>83</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="G5" t="s">
         <v>84</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="H5" t="s">
         <v>85</v>
       </c>
-      <c r="I5" s="15" t="s">
+      <c r="I5" t="s">
         <v>86</v>
       </c>
-      <c r="J5" s="15" t="s">
+      <c r="J5" t="s">
         <v>87</v>
       </c>
-      <c r="K5" s="16">
+      <c r="K5" s="12">
         <v>43984</v>
       </c>
-      <c r="L5" s="15" t="s">
+      <c r="L5" t="s">
         <v>88</v>
       </c>
     </row>
@@ -4298,37 +6464,37 @@
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" t="s">
         <v>89</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" t="s">
         <v>90</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" t="s">
         <v>91</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" t="s">
         <v>92</v>
       </c>
-      <c r="F6" s="15" t="s">
+      <c r="F6" t="s">
         <v>93</v>
       </c>
-      <c r="G6" s="15" t="s">
+      <c r="G6" t="s">
         <v>94</v>
       </c>
-      <c r="H6" s="15" t="s">
+      <c r="H6" t="s">
         <v>95</v>
       </c>
-      <c r="I6" s="15" t="s">
+      <c r="I6" t="s">
         <v>96</v>
       </c>
-      <c r="J6" s="15" t="s">
+      <c r="J6" t="s">
         <v>97</v>
       </c>
-      <c r="K6" s="16">
+      <c r="K6" s="12">
         <v>44303</v>
       </c>
-      <c r="L6" s="15" t="s">
+      <c r="L6" t="s">
         <v>98</v>
       </c>
     </row>
@@ -4336,37 +6502,37 @@
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" t="s">
         <v>99</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" t="s">
         <v>100</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="D7" t="s">
         <v>101</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" t="s">
         <v>102</v>
       </c>
-      <c r="F7" s="15" t="s">
+      <c r="F7" t="s">
         <v>103</v>
       </c>
-      <c r="G7" s="15" t="s">
+      <c r="G7" t="s">
         <v>104</v>
       </c>
-      <c r="H7" s="15" t="s">
+      <c r="H7" t="s">
         <v>105</v>
       </c>
-      <c r="I7" s="15" t="s">
+      <c r="I7" t="s">
         <v>106</v>
       </c>
-      <c r="J7" s="15" t="s">
+      <c r="J7" t="s">
         <v>107</v>
       </c>
-      <c r="K7" s="16">
+      <c r="K7" s="12">
         <v>43886</v>
       </c>
-      <c r="L7" s="15" t="s">
+      <c r="L7" t="s">
         <v>108</v>
       </c>
     </row>
@@ -4374,37 +6540,37 @@
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" t="s">
         <v>109</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" t="s">
         <v>110</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="D8" t="s">
         <v>111</v>
       </c>
-      <c r="E8" s="15" t="s">
+      <c r="E8" t="s">
         <v>112</v>
       </c>
-      <c r="F8" s="15" t="s">
+      <c r="F8" t="s">
         <v>113</v>
       </c>
-      <c r="G8" s="15" t="s">
+      <c r="G8" t="s">
         <v>114</v>
       </c>
-      <c r="H8" s="15" t="s">
+      <c r="H8" t="s">
         <v>115</v>
       </c>
-      <c r="I8" s="15" t="s">
+      <c r="I8" t="s">
         <v>116</v>
       </c>
-      <c r="J8" s="15" t="s">
+      <c r="J8" t="s">
         <v>117</v>
       </c>
-      <c r="K8" s="16">
+      <c r="K8" s="12">
         <v>44432</v>
       </c>
-      <c r="L8" s="15" t="s">
+      <c r="L8" t="s">
         <v>118</v>
       </c>
     </row>
@@ -4412,37 +6578,37 @@
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="B9" t="s">
         <v>119</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" t="s">
         <v>120</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="D9" t="s">
         <v>121</v>
       </c>
-      <c r="E9" s="15" t="s">
+      <c r="E9" t="s">
         <v>122</v>
       </c>
-      <c r="F9" s="15" t="s">
+      <c r="F9" t="s">
         <v>123</v>
       </c>
-      <c r="G9" s="15" t="s">
+      <c r="G9" t="s">
         <v>124</v>
       </c>
-      <c r="H9" s="15" t="s">
+      <c r="H9" t="s">
         <v>125</v>
       </c>
-      <c r="I9" s="15" t="s">
+      <c r="I9" t="s">
         <v>126</v>
       </c>
-      <c r="J9" s="15" t="s">
+      <c r="J9" t="s">
         <v>127</v>
       </c>
-      <c r="K9" s="16">
+      <c r="K9" s="12">
         <v>44298</v>
       </c>
-      <c r="L9" s="15" t="s">
+      <c r="L9" t="s">
         <v>128</v>
       </c>
     </row>
@@ -4450,37 +6616,37 @@
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" t="s">
         <v>129</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" t="s">
         <v>50</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="D10" t="s">
         <v>130</v>
       </c>
-      <c r="E10" s="15" t="s">
+      <c r="E10" t="s">
         <v>131</v>
       </c>
-      <c r="F10" s="15" t="s">
+      <c r="F10" t="s">
         <v>132</v>
       </c>
-      <c r="G10" s="15" t="s">
+      <c r="G10" t="s">
         <v>133</v>
       </c>
-      <c r="H10" s="15" t="s">
+      <c r="H10" t="s">
         <v>134</v>
       </c>
-      <c r="I10" s="15" t="s">
+      <c r="I10" t="s">
         <v>135</v>
       </c>
-      <c r="J10" s="15" t="s">
+      <c r="J10" t="s">
         <v>136</v>
       </c>
-      <c r="K10" s="16">
+      <c r="K10" s="12">
         <v>43843</v>
       </c>
-      <c r="L10" s="15" t="s">
+      <c r="L10" t="s">
         <v>137</v>
       </c>
     </row>
@@ -4488,37 +6654,37 @@
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="B11" t="s">
         <v>138</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" t="s">
         <v>139</v>
       </c>
-      <c r="D11" s="15" t="s">
+      <c r="D11" t="s">
         <v>140</v>
       </c>
-      <c r="E11" s="15" t="s">
+      <c r="E11" t="s">
         <v>141</v>
       </c>
-      <c r="F11" s="15" t="s">
+      <c r="F11" t="s">
         <v>142</v>
       </c>
-      <c r="G11" s="15" t="s">
+      <c r="G11" t="s">
         <v>143</v>
       </c>
-      <c r="H11" s="15" t="s">
+      <c r="H11" t="s">
         <v>144</v>
       </c>
-      <c r="I11" s="15" t="s">
+      <c r="I11" t="s">
         <v>145</v>
       </c>
-      <c r="J11" s="15" t="s">
+      <c r="J11" t="s">
         <v>146</v>
       </c>
-      <c r="K11" s="16">
+      <c r="K11" s="12">
         <v>44508</v>
       </c>
-      <c r="L11" s="15" t="s">
+      <c r="L11" t="s">
         <v>147</v>
       </c>
     </row>
@@ -4526,37 +6692,37 @@
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="B12" t="s">
         <v>148</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="C12" t="s">
         <v>149</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="D12" t="s">
         <v>150</v>
       </c>
-      <c r="E12" s="15" t="s">
+      <c r="E12" t="s">
         <v>151</v>
       </c>
-      <c r="F12" s="15" t="s">
+      <c r="F12" t="s">
         <v>152</v>
       </c>
-      <c r="G12" s="15" t="s">
+      <c r="G12" t="s">
         <v>153</v>
       </c>
-      <c r="H12" s="15" t="s">
+      <c r="H12" t="s">
         <v>154</v>
       </c>
-      <c r="I12" s="15" t="s">
+      <c r="I12" t="s">
         <v>155</v>
       </c>
-      <c r="J12" s="15" t="s">
+      <c r="J12" t="s">
         <v>156</v>
       </c>
-      <c r="K12" s="16">
+      <c r="K12" s="12">
         <v>44489</v>
       </c>
-      <c r="L12" s="15" t="s">
+      <c r="L12" t="s">
         <v>157</v>
       </c>
     </row>
@@ -4564,37 +6730,37 @@
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" t="s">
         <v>158</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" t="s">
         <v>159</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" t="s">
         <v>160</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="E13" t="s">
         <v>161</v>
       </c>
-      <c r="F13" s="15" t="s">
+      <c r="F13" t="s">
         <v>162</v>
       </c>
-      <c r="G13" s="15" t="s">
+      <c r="G13" t="s">
         <v>163</v>
       </c>
-      <c r="H13" s="15" t="s">
+      <c r="H13" t="s">
         <v>164</v>
       </c>
-      <c r="I13" s="15" t="s">
+      <c r="I13" t="s">
         <v>165</v>
       </c>
-      <c r="J13" s="15" t="s">
+      <c r="J13" t="s">
         <v>166</v>
       </c>
-      <c r="K13" s="16">
+      <c r="K13" s="12">
         <v>44164</v>
       </c>
-      <c r="L13" s="15" t="s">
+      <c r="L13" t="s">
         <v>167</v>
       </c>
     </row>
@@ -4602,37 +6768,37 @@
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" t="s">
         <v>168</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" t="s">
         <v>169</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="D14" t="s">
         <v>170</v>
       </c>
-      <c r="E14" s="15" t="s">
+      <c r="E14" t="s">
         <v>171</v>
       </c>
-      <c r="F14" s="15" t="s">
+      <c r="F14" t="s">
         <v>172</v>
       </c>
-      <c r="G14" s="15" t="s">
+      <c r="G14" t="s">
         <v>173</v>
       </c>
-      <c r="H14" s="15" t="s">
+      <c r="H14" t="s">
         <v>174</v>
       </c>
-      <c r="I14" s="15" t="s">
+      <c r="I14" t="s">
         <v>175</v>
       </c>
-      <c r="J14" s="15" t="s">
+      <c r="J14" t="s">
         <v>176</v>
       </c>
-      <c r="K14" s="16">
+      <c r="K14" s="12">
         <v>44532</v>
       </c>
-      <c r="L14" s="15" t="s">
+      <c r="L14" t="s">
         <v>177</v>
       </c>
     </row>
@@ -4640,37 +6806,37 @@
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="B15" t="s">
         <v>178</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C15" t="s">
         <v>179</v>
       </c>
-      <c r="D15" s="15" t="s">
+      <c r="D15" t="s">
         <v>180</v>
       </c>
-      <c r="E15" s="15" t="s">
+      <c r="E15" t="s">
         <v>181</v>
       </c>
-      <c r="F15" s="15" t="s">
+      <c r="F15" t="s">
         <v>182</v>
       </c>
-      <c r="G15" s="15" t="s">
+      <c r="G15" t="s">
         <v>183</v>
       </c>
-      <c r="H15" s="15" t="s">
+      <c r="H15" t="s">
         <v>184</v>
       </c>
-      <c r="I15" s="15" t="s">
+      <c r="I15" t="s">
         <v>185</v>
       </c>
-      <c r="J15" s="15" t="s">
+      <c r="J15" t="s">
         <v>186</v>
       </c>
-      <c r="K15" s="16">
+      <c r="K15" s="12">
         <v>44235</v>
       </c>
-      <c r="L15" s="15" t="s">
+      <c r="L15" t="s">
         <v>187</v>
       </c>
     </row>
@@ -4678,37 +6844,37 @@
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" s="15" t="s">
+      <c r="B16" t="s">
         <v>188</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="C16" t="s">
         <v>189</v>
       </c>
-      <c r="D16" s="15" t="s">
+      <c r="D16" t="s">
         <v>190</v>
       </c>
-      <c r="E16" s="15" t="s">
+      <c r="E16" t="s">
         <v>191</v>
       </c>
-      <c r="F16" s="15" t="s">
+      <c r="F16" t="s">
         <v>192</v>
       </c>
-      <c r="G16" s="15" t="s">
+      <c r="G16" t="s">
         <v>193</v>
       </c>
-      <c r="H16" s="15" t="s">
+      <c r="H16" t="s">
         <v>194</v>
       </c>
-      <c r="I16" s="15" t="s">
+      <c r="I16" t="s">
         <v>195</v>
       </c>
-      <c r="J16" s="15" t="s">
+      <c r="J16" t="s">
         <v>196</v>
       </c>
-      <c r="K16" s="16">
+      <c r="K16" s="12">
         <v>44587</v>
       </c>
-      <c r="L16" s="15" t="s">
+      <c r="L16" t="s">
         <v>197</v>
       </c>
     </row>
@@ -4716,37 +6882,37 @@
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="B17" t="s">
         <v>198</v>
       </c>
-      <c r="C17" s="15" t="s">
+      <c r="C17" t="s">
         <v>199</v>
       </c>
-      <c r="D17" s="15" t="s">
+      <c r="D17" t="s">
         <v>200</v>
       </c>
-      <c r="E17" s="15" t="s">
+      <c r="E17" t="s">
         <v>201</v>
       </c>
-      <c r="F17" s="15" t="s">
+      <c r="F17" t="s">
         <v>202</v>
       </c>
-      <c r="G17" s="15" t="s">
+      <c r="G17" t="s">
         <v>203</v>
       </c>
-      <c r="H17" s="15" t="s">
+      <c r="H17" t="s">
         <v>204</v>
       </c>
-      <c r="I17" s="15" t="s">
+      <c r="I17" t="s">
         <v>205</v>
       </c>
-      <c r="J17" s="15" t="s">
+      <c r="J17" t="s">
         <v>206</v>
       </c>
-      <c r="K17" s="16">
+      <c r="K17" s="12">
         <v>44663</v>
       </c>
-      <c r="L17" s="15" t="s">
+      <c r="L17" t="s">
         <v>207</v>
       </c>
     </row>
@@ -4754,37 +6920,37 @@
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" s="15" t="s">
+      <c r="B18" t="s">
         <v>208</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C18" t="s">
         <v>209</v>
       </c>
-      <c r="D18" s="15" t="s">
+      <c r="D18" t="s">
         <v>210</v>
       </c>
-      <c r="E18" s="15" t="s">
+      <c r="E18" t="s">
         <v>211</v>
       </c>
-      <c r="F18" s="15" t="s">
+      <c r="F18" t="s">
         <v>212</v>
       </c>
-      <c r="G18" s="15" t="s">
+      <c r="G18" t="s">
         <v>213</v>
       </c>
-      <c r="H18" s="15" t="s">
+      <c r="H18" t="s">
         <v>214</v>
       </c>
-      <c r="I18" s="15" t="s">
+      <c r="I18" t="s">
         <v>215</v>
       </c>
-      <c r="J18" s="15" t="s">
+      <c r="J18" t="s">
         <v>216</v>
       </c>
-      <c r="K18" s="16">
+      <c r="K18" s="12">
         <v>44265</v>
       </c>
-      <c r="L18" s="15" t="s">
+      <c r="L18" t="s">
         <v>217</v>
       </c>
     </row>
@@ -4792,37 +6958,37 @@
       <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="B19" t="s">
         <v>218</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="C19" t="s">
         <v>219</v>
       </c>
-      <c r="D19" s="15" t="s">
+      <c r="D19" t="s">
         <v>170</v>
       </c>
-      <c r="E19" s="15" t="s">
+      <c r="E19" t="s">
         <v>220</v>
       </c>
-      <c r="F19" s="15" t="s">
+      <c r="F19" t="s">
         <v>221</v>
       </c>
-      <c r="G19" s="15" t="s">
+      <c r="G19" t="s">
         <v>222</v>
       </c>
-      <c r="H19" s="15" t="s">
+      <c r="H19" t="s">
         <v>223</v>
       </c>
-      <c r="I19" s="15" t="s">
+      <c r="I19" t="s">
         <v>224</v>
       </c>
-      <c r="J19" s="15" t="s">
+      <c r="J19" t="s">
         <v>225</v>
       </c>
-      <c r="K19" s="16">
+      <c r="K19" s="12">
         <v>44646</v>
       </c>
-      <c r="L19" s="15" t="s">
+      <c r="L19" t="s">
         <v>226</v>
       </c>
     </row>
@@ -4830,37 +6996,37 @@
       <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" s="15" t="s">
+      <c r="B20" t="s">
         <v>227</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="C20" t="s">
         <v>228</v>
       </c>
-      <c r="D20" s="15" t="s">
+      <c r="D20" t="s">
         <v>229</v>
       </c>
-      <c r="E20" s="15" t="s">
+      <c r="E20" t="s">
         <v>230</v>
       </c>
-      <c r="F20" s="15" t="s">
+      <c r="F20" t="s">
         <v>231</v>
       </c>
-      <c r="G20" s="15" t="s">
+      <c r="G20" t="s">
         <v>232</v>
       </c>
-      <c r="H20" s="15" t="s">
+      <c r="H20" t="s">
         <v>233</v>
       </c>
-      <c r="I20" s="15" t="s">
+      <c r="I20" t="s">
         <v>234</v>
       </c>
-      <c r="J20" s="15" t="s">
+      <c r="J20" t="s">
         <v>235</v>
       </c>
-      <c r="K20" s="16">
+      <c r="K20" s="12">
         <v>44098</v>
       </c>
-      <c r="L20" s="15" t="s">
+      <c r="L20" t="s">
         <v>236</v>
       </c>
     </row>
@@ -4868,37 +7034,37 @@
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" s="15" t="s">
+      <c r="B21" t="s">
         <v>237</v>
       </c>
-      <c r="C21" s="15" t="s">
+      <c r="C21" t="s">
         <v>90</v>
       </c>
-      <c r="D21" s="15" t="s">
+      <c r="D21" t="s">
         <v>238</v>
       </c>
-      <c r="E21" s="15" t="s">
+      <c r="E21" t="s">
         <v>239</v>
       </c>
-      <c r="F21" s="15" t="s">
+      <c r="F21" t="s">
         <v>240</v>
       </c>
-      <c r="G21" s="15" t="s">
+      <c r="G21" t="s">
         <v>241</v>
       </c>
-      <c r="H21" s="15" t="s">
+      <c r="H21" t="s">
         <v>242</v>
       </c>
-      <c r="I21" s="15" t="s">
+      <c r="I21" t="s">
         <v>243</v>
       </c>
-      <c r="J21" s="15" t="s">
+      <c r="J21" t="s">
         <v>244</v>
       </c>
-      <c r="K21" s="16">
+      <c r="K21" s="12">
         <v>44463</v>
       </c>
-      <c r="L21" s="15" t="s">
+      <c r="L21" t="s">
         <v>245</v>
       </c>
     </row>
@@ -4906,37 +7072,37 @@
       <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" s="15" t="s">
+      <c r="B22" t="s">
         <v>246</v>
       </c>
-      <c r="C22" s="15" t="s">
+      <c r="C22" t="s">
         <v>247</v>
       </c>
-      <c r="D22" s="15" t="s">
+      <c r="D22" t="s">
         <v>248</v>
       </c>
-      <c r="E22" s="15" t="s">
+      <c r="E22" t="s">
         <v>249</v>
       </c>
-      <c r="F22" s="15" t="s">
+      <c r="F22" t="s">
         <v>250</v>
       </c>
-      <c r="G22" s="15" t="s">
+      <c r="G22" t="s">
         <v>251</v>
       </c>
-      <c r="H22" s="15" t="s">
+      <c r="H22" t="s">
         <v>252</v>
       </c>
-      <c r="I22" s="15" t="s">
+      <c r="I22" t="s">
         <v>253</v>
       </c>
-      <c r="J22" s="15" t="s">
+      <c r="J22" t="s">
         <v>254</v>
       </c>
-      <c r="K22" s="16">
+      <c r="K22" s="12">
         <v>44573</v>
       </c>
-      <c r="L22" s="15" t="s">
+      <c r="L22" t="s">
         <v>255</v>
       </c>
     </row>
@@ -4944,37 +7110,37 @@
       <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" s="15" t="s">
+      <c r="B23" t="s">
         <v>256</v>
       </c>
-      <c r="C23" s="15" t="s">
+      <c r="C23" t="s">
         <v>257</v>
       </c>
-      <c r="D23" s="15" t="s">
+      <c r="D23" t="s">
         <v>258</v>
       </c>
-      <c r="E23" s="15" t="s">
+      <c r="E23" t="s">
         <v>259</v>
       </c>
-      <c r="F23" s="15" t="s">
+      <c r="F23" t="s">
         <v>260</v>
       </c>
-      <c r="G23" s="15" t="s">
+      <c r="G23" t="s">
         <v>261</v>
       </c>
-      <c r="H23" s="15" t="s">
+      <c r="H23" t="s">
         <v>262</v>
       </c>
-      <c r="I23" s="15" t="s">
+      <c r="I23" t="s">
         <v>263</v>
       </c>
-      <c r="J23" s="15" t="s">
+      <c r="J23" t="s">
         <v>264</v>
       </c>
-      <c r="K23" s="16">
+      <c r="K23" s="12">
         <v>44089</v>
       </c>
-      <c r="L23" s="15" t="s">
+      <c r="L23" t="s">
         <v>265</v>
       </c>
     </row>
@@ -4982,37 +7148,37 @@
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" s="15" t="s">
+      <c r="B24" t="s">
         <v>266</v>
       </c>
-      <c r="C24" s="15" t="s">
+      <c r="C24" t="s">
         <v>267</v>
       </c>
-      <c r="D24" s="15" t="s">
+      <c r="D24" t="s">
         <v>268</v>
       </c>
-      <c r="E24" s="15" t="s">
+      <c r="E24" t="s">
         <v>269</v>
       </c>
-      <c r="F24" s="15" t="s">
+      <c r="F24" t="s">
         <v>270</v>
       </c>
-      <c r="G24" s="15" t="s">
+      <c r="G24" t="s">
         <v>271</v>
       </c>
-      <c r="H24" s="15" t="s">
+      <c r="H24" t="s">
         <v>272</v>
       </c>
-      <c r="I24" s="15" t="s">
+      <c r="I24" t="s">
         <v>273</v>
       </c>
-      <c r="J24" s="15" t="s">
+      <c r="J24" t="s">
         <v>274</v>
       </c>
-      <c r="K24" s="16">
+      <c r="K24" s="12">
         <v>44062</v>
       </c>
-      <c r="L24" s="15" t="s">
+      <c r="L24" t="s">
         <v>275</v>
       </c>
     </row>
@@ -5020,37 +7186,37 @@
       <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" s="15" t="s">
+      <c r="B25" t="s">
         <v>276</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="C25" t="s">
         <v>277</v>
       </c>
-      <c r="D25" s="15" t="s">
+      <c r="D25" t="s">
         <v>278</v>
       </c>
-      <c r="E25" s="15" t="s">
+      <c r="E25" t="s">
         <v>279</v>
       </c>
-      <c r="F25" s="15" t="s">
+      <c r="F25" t="s">
         <v>280</v>
       </c>
-      <c r="G25" s="15" t="s">
+      <c r="G25" t="s">
         <v>281</v>
       </c>
-      <c r="H25" s="15" t="s">
+      <c r="H25" t="s">
         <v>282</v>
       </c>
-      <c r="I25" s="15" t="s">
+      <c r="I25" t="s">
         <v>283</v>
       </c>
-      <c r="J25" s="15" t="s">
+      <c r="J25" t="s">
         <v>284</v>
       </c>
-      <c r="K25" s="16">
+      <c r="K25" s="12">
         <v>44082</v>
       </c>
-      <c r="L25" s="15" t="s">
+      <c r="L25" t="s">
         <v>285</v>
       </c>
     </row>
@@ -5058,37 +7224,37 @@
       <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" s="15" t="s">
+      <c r="B26" t="s">
         <v>286</v>
       </c>
-      <c r="C26" s="15" t="s">
+      <c r="C26" t="s">
         <v>287</v>
       </c>
-      <c r="D26" s="15" t="s">
+      <c r="D26" t="s">
         <v>288</v>
       </c>
-      <c r="E26" s="15" t="s">
+      <c r="E26" t="s">
         <v>289</v>
       </c>
-      <c r="F26" s="15" t="s">
+      <c r="F26" t="s">
         <v>290</v>
       </c>
-      <c r="G26" s="15" t="s">
+      <c r="G26" t="s">
         <v>291</v>
       </c>
-      <c r="H26" s="15" t="s">
+      <c r="H26" t="s">
         <v>292</v>
       </c>
-      <c r="I26" s="15" t="s">
+      <c r="I26" t="s">
         <v>293</v>
       </c>
-      <c r="J26" s="15" t="s">
+      <c r="J26" t="s">
         <v>294</v>
       </c>
-      <c r="K26" s="16">
+      <c r="K26" s="12">
         <v>44292</v>
       </c>
-      <c r="L26" s="15" t="s">
+      <c r="L26" t="s">
         <v>295</v>
       </c>
     </row>
@@ -5096,37 +7262,37 @@
       <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" s="15" t="s">
+      <c r="B27" t="s">
         <v>296</v>
       </c>
-      <c r="C27" s="15" t="s">
+      <c r="C27" t="s">
         <v>297</v>
       </c>
-      <c r="D27" s="15" t="s">
+      <c r="D27" t="s">
         <v>298</v>
       </c>
-      <c r="E27" s="15" t="s">
+      <c r="E27" t="s">
         <v>299</v>
       </c>
-      <c r="F27" s="15" t="s">
+      <c r="F27" t="s">
         <v>300</v>
       </c>
-      <c r="G27" s="15" t="s">
+      <c r="G27" t="s">
         <v>301</v>
       </c>
-      <c r="H27" s="15" t="s">
+      <c r="H27" t="s">
         <v>302</v>
       </c>
-      <c r="I27" s="15" t="s">
+      <c r="I27" t="s">
         <v>303</v>
       </c>
-      <c r="J27" s="15" t="s">
+      <c r="J27" t="s">
         <v>304</v>
       </c>
-      <c r="K27" s="16">
+      <c r="K27" s="12">
         <v>44705</v>
       </c>
-      <c r="L27" s="15" t="s">
+      <c r="L27" t="s">
         <v>305</v>
       </c>
     </row>
@@ -5134,37 +7300,37 @@
       <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28" s="15" t="s">
+      <c r="B28" t="s">
         <v>306</v>
       </c>
-      <c r="C28" s="15" t="s">
+      <c r="C28" t="s">
         <v>307</v>
       </c>
-      <c r="D28" s="15" t="s">
+      <c r="D28" t="s">
         <v>308</v>
       </c>
-      <c r="E28" s="15" t="s">
+      <c r="E28" t="s">
         <v>309</v>
       </c>
-      <c r="F28" s="15" t="s">
+      <c r="F28" t="s">
         <v>310</v>
       </c>
-      <c r="G28" s="15" t="s">
+      <c r="G28" t="s">
         <v>311</v>
       </c>
-      <c r="H28" s="15" t="s">
+      <c r="H28" t="s">
         <v>312</v>
       </c>
-      <c r="I28" s="15" t="s">
+      <c r="I28" t="s">
         <v>313</v>
       </c>
-      <c r="J28" s="15" t="s">
+      <c r="J28" t="s">
         <v>314</v>
       </c>
-      <c r="K28" s="16">
+      <c r="K28" s="12">
         <v>44612</v>
       </c>
-      <c r="L28" s="15" t="s">
+      <c r="L28" t="s">
         <v>315</v>
       </c>
     </row>
@@ -5172,37 +7338,37 @@
       <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29" s="15" t="s">
+      <c r="B29" t="s">
         <v>316</v>
       </c>
-      <c r="C29" s="15" t="s">
+      <c r="C29" t="s">
         <v>317</v>
       </c>
-      <c r="D29" s="15" t="s">
+      <c r="D29" t="s">
         <v>318</v>
       </c>
-      <c r="E29" s="15" t="s">
+      <c r="E29" t="s">
         <v>319</v>
       </c>
-      <c r="F29" s="15" t="s">
+      <c r="F29" t="s">
         <v>320</v>
       </c>
-      <c r="G29" s="15" t="s">
+      <c r="G29" t="s">
         <v>321</v>
       </c>
-      <c r="H29" s="15" t="s">
+      <c r="H29" t="s">
         <v>322</v>
       </c>
-      <c r="I29" s="15" t="s">
+      <c r="I29" t="s">
         <v>323</v>
       </c>
-      <c r="J29" s="15" t="s">
+      <c r="J29" t="s">
         <v>324</v>
       </c>
-      <c r="K29" s="16">
+      <c r="K29" s="12">
         <v>44707</v>
       </c>
-      <c r="L29" s="15" t="s">
+      <c r="L29" t="s">
         <v>325</v>
       </c>
     </row>
@@ -5210,37 +7376,37 @@
       <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30" s="15" t="s">
+      <c r="B30" t="s">
         <v>326</v>
       </c>
-      <c r="C30" s="15" t="s">
+      <c r="C30" t="s">
         <v>327</v>
       </c>
-      <c r="D30" s="15" t="s">
+      <c r="D30" t="s">
         <v>328</v>
       </c>
-      <c r="E30" s="15" t="s">
+      <c r="E30" t="s">
         <v>329</v>
       </c>
-      <c r="F30" s="15" t="s">
+      <c r="F30" t="s">
         <v>330</v>
       </c>
-      <c r="G30" s="15" t="s">
+      <c r="G30" t="s">
         <v>331</v>
       </c>
-      <c r="H30" s="15" t="s">
+      <c r="H30" t="s">
         <v>332</v>
       </c>
-      <c r="I30" s="15" t="s">
+      <c r="I30" t="s">
         <v>333</v>
       </c>
-      <c r="J30" s="15" t="s">
+      <c r="J30" t="s">
         <v>334</v>
       </c>
-      <c r="K30" s="16">
+      <c r="K30" s="12">
         <v>44042</v>
       </c>
-      <c r="L30" s="15" t="s">
+      <c r="L30" t="s">
         <v>335</v>
       </c>
     </row>
@@ -5248,37 +7414,37 @@
       <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31" s="15" t="s">
+      <c r="B31" t="s">
         <v>336</v>
       </c>
-      <c r="C31" s="15" t="s">
+      <c r="C31" t="s">
         <v>337</v>
       </c>
-      <c r="D31" s="15" t="s">
+      <c r="D31" t="s">
         <v>338</v>
       </c>
-      <c r="E31" s="15" t="s">
+      <c r="E31" t="s">
         <v>339</v>
       </c>
-      <c r="F31" s="15" t="s">
+      <c r="F31" t="s">
         <v>340</v>
       </c>
-      <c r="G31" s="15" t="s">
+      <c r="G31" t="s">
         <v>341</v>
       </c>
-      <c r="H31" s="15" t="s">
+      <c r="H31" t="s">
         <v>342</v>
       </c>
-      <c r="I31" s="15" t="s">
+      <c r="I31" t="s">
         <v>343</v>
       </c>
-      <c r="J31" s="15" t="s">
+      <c r="J31" t="s">
         <v>344</v>
       </c>
-      <c r="K31" s="16">
+      <c r="K31" s="12">
         <v>43947</v>
       </c>
-      <c r="L31" s="15" t="s">
+      <c r="L31" t="s">
         <v>345</v>
       </c>
     </row>
@@ -5286,37 +7452,37 @@
       <c r="A32">
         <v>31</v>
       </c>
-      <c r="B32" s="15" t="s">
+      <c r="B32" t="s">
         <v>346</v>
       </c>
-      <c r="C32" s="15" t="s">
+      <c r="C32" t="s">
         <v>347</v>
       </c>
-      <c r="D32" s="15" t="s">
+      <c r="D32" t="s">
         <v>348</v>
       </c>
-      <c r="E32" s="15" t="s">
+      <c r="E32" t="s">
         <v>349</v>
       </c>
-      <c r="F32" s="15" t="s">
+      <c r="F32" t="s">
         <v>350</v>
       </c>
-      <c r="G32" s="15" t="s">
+      <c r="G32" t="s">
         <v>351</v>
       </c>
-      <c r="H32" s="15" t="s">
+      <c r="H32" t="s">
         <v>352</v>
       </c>
-      <c r="I32" s="15" t="s">
+      <c r="I32" t="s">
         <v>353</v>
       </c>
-      <c r="J32" s="15" t="s">
+      <c r="J32" t="s">
         <v>354</v>
       </c>
-      <c r="K32" s="16">
+      <c r="K32" s="12">
         <v>44454</v>
       </c>
-      <c r="L32" s="15" t="s">
+      <c r="L32" t="s">
         <v>355</v>
       </c>
     </row>
@@ -5324,37 +7490,37 @@
       <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33" s="15" t="s">
+      <c r="B33" t="s">
         <v>356</v>
       </c>
-      <c r="C33" s="15" t="s">
+      <c r="C33" t="s">
         <v>357</v>
       </c>
-      <c r="D33" s="15" t="s">
+      <c r="D33" t="s">
         <v>358</v>
       </c>
-      <c r="E33" s="15" t="s">
+      <c r="E33" t="s">
         <v>359</v>
       </c>
-      <c r="F33" s="15" t="s">
+      <c r="F33" t="s">
         <v>360</v>
       </c>
-      <c r="G33" s="15" t="s">
+      <c r="G33" t="s">
         <v>361</v>
       </c>
-      <c r="H33" s="15" t="s">
+      <c r="H33" t="s">
         <v>362</v>
       </c>
-      <c r="I33" s="15" t="s">
+      <c r="I33" t="s">
         <v>363</v>
       </c>
-      <c r="J33" s="15" t="s">
+      <c r="J33" t="s">
         <v>364</v>
       </c>
-      <c r="K33" s="16">
+      <c r="K33" s="12">
         <v>44574</v>
       </c>
-      <c r="L33" s="15" t="s">
+      <c r="L33" t="s">
         <v>365</v>
       </c>
     </row>
@@ -5362,37 +7528,37 @@
       <c r="A34">
         <v>33</v>
       </c>
-      <c r="B34" s="15" t="s">
+      <c r="B34" t="s">
         <v>366</v>
       </c>
-      <c r="C34" s="15" t="s">
+      <c r="C34" t="s">
         <v>367</v>
       </c>
-      <c r="D34" s="15" t="s">
+      <c r="D34" t="s">
         <v>368</v>
       </c>
-      <c r="E34" s="15" t="s">
+      <c r="E34" t="s">
         <v>369</v>
       </c>
-      <c r="F34" s="15" t="s">
+      <c r="F34" t="s">
         <v>370</v>
       </c>
-      <c r="G34" s="15" t="s">
+      <c r="G34" t="s">
         <v>371</v>
       </c>
-      <c r="H34" s="15" t="s">
+      <c r="H34" t="s">
         <v>372</v>
       </c>
-      <c r="I34" s="15" t="s">
+      <c r="I34" t="s">
         <v>373</v>
       </c>
-      <c r="J34" s="15" t="s">
+      <c r="J34" t="s">
         <v>374</v>
       </c>
-      <c r="K34" s="16">
+      <c r="K34" s="12">
         <v>44310</v>
       </c>
-      <c r="L34" s="15" t="s">
+      <c r="L34" t="s">
         <v>375</v>
       </c>
     </row>
@@ -5400,37 +7566,37 @@
       <c r="A35">
         <v>34</v>
       </c>
-      <c r="B35" s="15" t="s">
+      <c r="B35" t="s">
         <v>376</v>
       </c>
-      <c r="C35" s="15" t="s">
+      <c r="C35" t="s">
         <v>377</v>
       </c>
-      <c r="D35" s="15" t="s">
+      <c r="D35" t="s">
         <v>378</v>
       </c>
-      <c r="E35" s="15" t="s">
+      <c r="E35" t="s">
         <v>379</v>
       </c>
-      <c r="F35" s="15" t="s">
+      <c r="F35" t="s">
         <v>380</v>
       </c>
-      <c r="G35" s="15" t="s">
+      <c r="G35" t="s">
         <v>381</v>
       </c>
-      <c r="H35" s="15" t="s">
+      <c r="H35" t="s">
         <v>382</v>
       </c>
-      <c r="I35" s="15" t="s">
+      <c r="I35" t="s">
         <v>383</v>
       </c>
-      <c r="J35" s="15" t="s">
+      <c r="J35" t="s">
         <v>384</v>
       </c>
-      <c r="K35" s="16">
+      <c r="K35" s="12">
         <v>44460</v>
       </c>
-      <c r="L35" s="15" t="s">
+      <c r="L35" t="s">
         <v>385</v>
       </c>
     </row>
@@ -5438,37 +7604,37 @@
       <c r="A36">
         <v>35</v>
       </c>
-      <c r="B36" s="15" t="s">
+      <c r="B36" t="s">
         <v>386</v>
       </c>
-      <c r="C36" s="15" t="s">
+      <c r="C36" t="s">
         <v>189</v>
       </c>
-      <c r="D36" s="15" t="s">
+      <c r="D36" t="s">
         <v>387</v>
       </c>
-      <c r="E36" s="15" t="s">
+      <c r="E36" t="s">
         <v>388</v>
       </c>
-      <c r="F36" s="15" t="s">
+      <c r="F36" t="s">
         <v>389</v>
       </c>
-      <c r="G36" s="15" t="s">
+      <c r="G36" t="s">
         <v>390</v>
       </c>
-      <c r="H36" s="15" t="s">
+      <c r="H36" t="s">
         <v>391</v>
       </c>
-      <c r="I36" s="15" t="s">
+      <c r="I36" t="s">
         <v>392</v>
       </c>
-      <c r="J36" s="15" t="s">
+      <c r="J36" t="s">
         <v>393</v>
       </c>
-      <c r="K36" s="16">
+      <c r="K36" s="12">
         <v>44503</v>
       </c>
-      <c r="L36" s="15" t="s">
+      <c r="L36" t="s">
         <v>394</v>
       </c>
     </row>
@@ -5476,37 +7642,37 @@
       <c r="A37">
         <v>36</v>
       </c>
-      <c r="B37" s="15" t="s">
+      <c r="B37" t="s">
         <v>395</v>
       </c>
-      <c r="C37" s="15" t="s">
+      <c r="C37" t="s">
         <v>396</v>
       </c>
-      <c r="D37" s="15" t="s">
+      <c r="D37" t="s">
         <v>397</v>
       </c>
-      <c r="E37" s="15" t="s">
+      <c r="E37" t="s">
         <v>398</v>
       </c>
-      <c r="F37" s="15" t="s">
+      <c r="F37" t="s">
         <v>399</v>
       </c>
-      <c r="G37" s="15" t="s">
+      <c r="G37" t="s">
         <v>400</v>
       </c>
-      <c r="H37" s="15" t="s">
+      <c r="H37" t="s">
         <v>401</v>
       </c>
-      <c r="I37" s="15" t="s">
+      <c r="I37" t="s">
         <v>402</v>
       </c>
-      <c r="J37" s="15" t="s">
+      <c r="J37" t="s">
         <v>403</v>
       </c>
-      <c r="K37" s="16">
+      <c r="K37" s="12">
         <v>44565</v>
       </c>
-      <c r="L37" s="15" t="s">
+      <c r="L37" t="s">
         <v>404</v>
       </c>
     </row>
@@ -5514,37 +7680,37 @@
       <c r="A38">
         <v>37</v>
       </c>
-      <c r="B38" s="15" t="s">
+      <c r="B38" t="s">
         <v>405</v>
       </c>
-      <c r="C38" s="15" t="s">
+      <c r="C38" t="s">
         <v>406</v>
       </c>
-      <c r="D38" s="15" t="s">
+      <c r="D38" t="s">
         <v>407</v>
       </c>
-      <c r="E38" s="15" t="s">
+      <c r="E38" t="s">
         <v>408</v>
       </c>
-      <c r="F38" s="15" t="s">
+      <c r="F38" t="s">
         <v>409</v>
       </c>
-      <c r="G38" s="15" t="s">
+      <c r="G38" t="s">
         <v>410</v>
       </c>
-      <c r="H38" s="15" t="s">
+      <c r="H38" t="s">
         <v>411</v>
       </c>
-      <c r="I38" s="15" t="s">
+      <c r="I38" t="s">
         <v>412</v>
       </c>
-      <c r="J38" s="15" t="s">
+      <c r="J38" t="s">
         <v>413</v>
       </c>
-      <c r="K38" s="16">
+      <c r="K38" s="12">
         <v>44418</v>
       </c>
-      <c r="L38" s="15" t="s">
+      <c r="L38" t="s">
         <v>414</v>
       </c>
     </row>
@@ -5552,37 +7718,37 @@
       <c r="A39">
         <v>38</v>
       </c>
-      <c r="B39" s="15" t="s">
+      <c r="B39" t="s">
         <v>415</v>
       </c>
-      <c r="C39" s="15" t="s">
+      <c r="C39" t="s">
         <v>416</v>
       </c>
-      <c r="D39" s="15" t="s">
+      <c r="D39" t="s">
         <v>417</v>
       </c>
-      <c r="E39" s="15" t="s">
+      <c r="E39" t="s">
         <v>418</v>
       </c>
-      <c r="F39" s="15" t="s">
+      <c r="F39" t="s">
         <v>419</v>
       </c>
-      <c r="G39" s="15" t="s">
+      <c r="G39" t="s">
         <v>420</v>
       </c>
-      <c r="H39" s="15" t="s">
+      <c r="H39" t="s">
         <v>421</v>
       </c>
-      <c r="I39" s="15" t="s">
+      <c r="I39" t="s">
         <v>422</v>
       </c>
-      <c r="J39" s="15" t="s">
+      <c r="J39" t="s">
         <v>423</v>
       </c>
-      <c r="K39" s="16">
+      <c r="K39" s="12">
         <v>44251</v>
       </c>
-      <c r="L39" s="15" t="s">
+      <c r="L39" t="s">
         <v>424</v>
       </c>
     </row>
@@ -5590,37 +7756,37 @@
       <c r="A40">
         <v>39</v>
       </c>
-      <c r="B40" s="15" t="s">
+      <c r="B40" t="s">
         <v>425</v>
       </c>
-      <c r="C40" s="15" t="s">
+      <c r="C40" t="s">
         <v>426</v>
       </c>
-      <c r="D40" s="15" t="s">
+      <c r="D40" t="s">
         <v>427</v>
       </c>
-      <c r="E40" s="15" t="s">
+      <c r="E40" t="s">
         <v>428</v>
       </c>
-      <c r="F40" s="15" t="s">
+      <c r="F40" t="s">
         <v>429</v>
       </c>
-      <c r="G40" s="15" t="s">
+      <c r="G40" t="s">
         <v>430</v>
       </c>
-      <c r="H40" s="15" t="s">
+      <c r="H40" t="s">
         <v>431</v>
       </c>
-      <c r="I40" s="15" t="s">
+      <c r="I40" t="s">
         <v>432</v>
       </c>
-      <c r="J40" s="15" t="s">
+      <c r="J40" t="s">
         <v>433</v>
       </c>
-      <c r="K40" s="16">
+      <c r="K40" s="12">
         <v>44491</v>
       </c>
-      <c r="L40" s="15" t="s">
+      <c r="L40" t="s">
         <v>434</v>
       </c>
     </row>
@@ -5628,37 +7794,37 @@
       <c r="A41">
         <v>40</v>
       </c>
-      <c r="B41" s="15" t="s">
+      <c r="B41" t="s">
         <v>435</v>
       </c>
-      <c r="C41" s="15" t="s">
+      <c r="C41" t="s">
         <v>436</v>
       </c>
-      <c r="D41" s="15" t="s">
+      <c r="D41" t="s">
         <v>437</v>
       </c>
-      <c r="E41" s="15" t="s">
+      <c r="E41" t="s">
         <v>438</v>
       </c>
-      <c r="F41" s="15" t="s">
+      <c r="F41" t="s">
         <v>439</v>
       </c>
-      <c r="G41" s="15" t="s">
+      <c r="G41" t="s">
         <v>440</v>
       </c>
-      <c r="H41" s="15" t="s">
+      <c r="H41" t="s">
         <v>441</v>
       </c>
-      <c r="I41" s="15" t="s">
+      <c r="I41" t="s">
         <v>442</v>
       </c>
-      <c r="J41" s="15" t="s">
+      <c r="J41" t="s">
         <v>443</v>
       </c>
-      <c r="K41" s="16">
+      <c r="K41" s="12">
         <v>44501</v>
       </c>
-      <c r="L41" s="15" t="s">
+      <c r="L41" t="s">
         <v>444</v>
       </c>
     </row>
@@ -5666,37 +7832,37 @@
       <c r="A42">
         <v>41</v>
       </c>
-      <c r="B42" s="15" t="s">
+      <c r="B42" t="s">
         <v>445</v>
       </c>
-      <c r="C42" s="15" t="s">
+      <c r="C42" t="s">
         <v>446</v>
       </c>
-      <c r="D42" s="15" t="s">
+      <c r="D42" t="s">
         <v>447</v>
       </c>
-      <c r="E42" s="15" t="s">
+      <c r="E42" t="s">
         <v>448</v>
       </c>
-      <c r="F42" s="15" t="s">
+      <c r="F42" t="s">
         <v>449</v>
       </c>
-      <c r="G42" s="15" t="s">
+      <c r="G42" t="s">
         <v>84</v>
       </c>
-      <c r="H42" s="15" t="s">
+      <c r="H42" t="s">
         <v>450</v>
       </c>
-      <c r="I42" s="15" t="s">
+      <c r="I42" t="s">
         <v>451</v>
       </c>
-      <c r="J42" s="15" t="s">
+      <c r="J42" t="s">
         <v>452</v>
       </c>
-      <c r="K42" s="16">
+      <c r="K42" s="12">
         <v>44114</v>
       </c>
-      <c r="L42" s="15" t="s">
+      <c r="L42" t="s">
         <v>453</v>
       </c>
     </row>
@@ -5704,37 +7870,37 @@
       <c r="A43">
         <v>42</v>
       </c>
-      <c r="B43" s="15" t="s">
+      <c r="B43" t="s">
         <v>454</v>
       </c>
-      <c r="C43" s="15" t="s">
+      <c r="C43" t="s">
         <v>455</v>
       </c>
-      <c r="D43" s="15" t="s">
+      <c r="D43" t="s">
         <v>456</v>
       </c>
-      <c r="E43" s="15" t="s">
+      <c r="E43" t="s">
         <v>457</v>
       </c>
-      <c r="F43" s="15" t="s">
+      <c r="F43" t="s">
         <v>458</v>
       </c>
-      <c r="G43" s="15" t="s">
+      <c r="G43" t="s">
         <v>459</v>
       </c>
-      <c r="H43" s="15" t="s">
+      <c r="H43" t="s">
         <v>460</v>
       </c>
-      <c r="I43" s="15" t="s">
+      <c r="I43" t="s">
         <v>461</v>
       </c>
-      <c r="J43" s="15" t="s">
+      <c r="J43" t="s">
         <v>462</v>
       </c>
-      <c r="K43" s="16">
+      <c r="K43" s="12">
         <v>44447</v>
       </c>
-      <c r="L43" s="15" t="s">
+      <c r="L43" t="s">
         <v>463</v>
       </c>
     </row>
@@ -5742,37 +7908,37 @@
       <c r="A44">
         <v>43</v>
       </c>
-      <c r="B44" s="15" t="s">
+      <c r="B44" t="s">
         <v>464</v>
       </c>
-      <c r="C44" s="15" t="s">
+      <c r="C44" t="s">
         <v>465</v>
       </c>
-      <c r="D44" s="15" t="s">
+      <c r="D44" t="s">
         <v>466</v>
       </c>
-      <c r="E44" s="15" t="s">
+      <c r="E44" t="s">
         <v>467</v>
       </c>
-      <c r="F44" s="15" t="s">
+      <c r="F44" t="s">
         <v>468</v>
       </c>
-      <c r="G44" s="15" t="s">
+      <c r="G44" t="s">
         <v>469</v>
       </c>
-      <c r="H44" s="15" t="s">
+      <c r="H44" t="s">
         <v>470</v>
       </c>
-      <c r="I44" s="15" t="s">
+      <c r="I44" t="s">
         <v>471</v>
       </c>
-      <c r="J44" s="15" t="s">
+      <c r="J44" t="s">
         <v>472</v>
       </c>
-      <c r="K44" s="16">
+      <c r="K44" s="12">
         <v>44178</v>
       </c>
-      <c r="L44" s="15" t="s">
+      <c r="L44" t="s">
         <v>473</v>
       </c>
     </row>
@@ -5780,37 +7946,37 @@
       <c r="A45">
         <v>44</v>
       </c>
-      <c r="B45" s="15" t="s">
+      <c r="B45" t="s">
         <v>474</v>
       </c>
-      <c r="C45" s="15" t="s">
+      <c r="C45" t="s">
         <v>475</v>
       </c>
-      <c r="D45" s="15" t="s">
+      <c r="D45" t="s">
         <v>476</v>
       </c>
-      <c r="E45" s="15" t="s">
+      <c r="E45" t="s">
         <v>477</v>
       </c>
-      <c r="F45" s="15" t="s">
+      <c r="F45" t="s">
         <v>478</v>
       </c>
-      <c r="G45" s="15" t="s">
+      <c r="G45" t="s">
         <v>124</v>
       </c>
-      <c r="H45" s="15" t="s">
+      <c r="H45" t="s">
         <v>479</v>
       </c>
-      <c r="I45" s="15" t="s">
+      <c r="I45" t="s">
         <v>480</v>
       </c>
-      <c r="J45" s="15" t="s">
+      <c r="J45" t="s">
         <v>481</v>
       </c>
-      <c r="K45" s="16">
+      <c r="K45" s="12">
         <v>44696</v>
       </c>
-      <c r="L45" s="15" t="s">
+      <c r="L45" t="s">
         <v>482</v>
       </c>
     </row>
@@ -5818,37 +7984,37 @@
       <c r="A46">
         <v>45</v>
       </c>
-      <c r="B46" s="15" t="s">
+      <c r="B46" t="s">
         <v>483</v>
       </c>
-      <c r="C46" s="15" t="s">
+      <c r="C46" t="s">
         <v>484</v>
       </c>
-      <c r="D46" s="15" t="s">
+      <c r="D46" t="s">
         <v>485</v>
       </c>
-      <c r="E46" s="15" t="s">
+      <c r="E46" t="s">
         <v>486</v>
       </c>
-      <c r="F46" s="15" t="s">
+      <c r="F46" t="s">
         <v>487</v>
       </c>
-      <c r="G46" s="15" t="s">
+      <c r="G46" t="s">
         <v>488</v>
       </c>
-      <c r="H46" s="15" t="s">
+      <c r="H46" t="s">
         <v>489</v>
       </c>
-      <c r="I46" s="15" t="s">
+      <c r="I46" t="s">
         <v>490</v>
       </c>
-      <c r="J46" s="15" t="s">
+      <c r="J46" t="s">
         <v>491</v>
       </c>
-      <c r="K46" s="16">
+      <c r="K46" s="12">
         <v>44536</v>
       </c>
-      <c r="L46" s="15" t="s">
+      <c r="L46" t="s">
         <v>492</v>
       </c>
     </row>
@@ -5856,37 +8022,37 @@
       <c r="A47">
         <v>46</v>
       </c>
-      <c r="B47" s="15" t="s">
+      <c r="B47" t="s">
         <v>493</v>
       </c>
-      <c r="C47" s="15" t="s">
+      <c r="C47" t="s">
         <v>494</v>
       </c>
-      <c r="D47" s="15" t="s">
+      <c r="D47" t="s">
         <v>495</v>
       </c>
-      <c r="E47" s="15" t="s">
+      <c r="E47" t="s">
         <v>496</v>
       </c>
-      <c r="F47" s="15" t="s">
+      <c r="F47" t="s">
         <v>497</v>
       </c>
-      <c r="G47" s="15" t="s">
+      <c r="G47" t="s">
         <v>498</v>
       </c>
-      <c r="H47" s="15" t="s">
+      <c r="H47" t="s">
         <v>499</v>
       </c>
-      <c r="I47" s="15" t="s">
+      <c r="I47" t="s">
         <v>500</v>
       </c>
-      <c r="J47" s="15" t="s">
+      <c r="J47" t="s">
         <v>501</v>
       </c>
-      <c r="K47" s="16">
+      <c r="K47" s="12">
         <v>44013</v>
       </c>
-      <c r="L47" s="15" t="s">
+      <c r="L47" t="s">
         <v>502</v>
       </c>
     </row>
@@ -5894,37 +8060,37 @@
       <c r="A48">
         <v>47</v>
       </c>
-      <c r="B48" s="15" t="s">
+      <c r="B48" t="s">
         <v>503</v>
       </c>
-      <c r="C48" s="15" t="s">
+      <c r="C48" t="s">
         <v>504</v>
       </c>
-      <c r="D48" s="15" t="s">
+      <c r="D48" t="s">
         <v>505</v>
       </c>
-      <c r="E48" s="15" t="s">
+      <c r="E48" t="s">
         <v>506</v>
       </c>
-      <c r="F48" s="15" t="s">
+      <c r="F48" t="s">
         <v>507</v>
       </c>
-      <c r="G48" s="15" t="s">
+      <c r="G48" t="s">
         <v>508</v>
       </c>
-      <c r="H48" s="15" t="s">
+      <c r="H48" t="s">
         <v>509</v>
       </c>
-      <c r="I48" s="15" t="s">
+      <c r="I48" t="s">
         <v>510</v>
       </c>
-      <c r="J48" s="15" t="s">
+      <c r="J48" t="s">
         <v>511</v>
       </c>
-      <c r="K48" s="16">
+      <c r="K48" s="12">
         <v>43944</v>
       </c>
-      <c r="L48" s="15" t="s">
+      <c r="L48" t="s">
         <v>512</v>
       </c>
     </row>
@@ -5932,37 +8098,37 @@
       <c r="A49">
         <v>48</v>
       </c>
-      <c r="B49" s="15" t="s">
+      <c r="B49" t="s">
         <v>513</v>
       </c>
-      <c r="C49" s="15" t="s">
+      <c r="C49" t="s">
         <v>514</v>
       </c>
-      <c r="D49" s="15" t="s">
+      <c r="D49" t="s">
         <v>515</v>
       </c>
-      <c r="E49" s="15" t="s">
+      <c r="E49" t="s">
         <v>516</v>
       </c>
-      <c r="F49" s="15" t="s">
+      <c r="F49" t="s">
         <v>517</v>
       </c>
-      <c r="G49" s="15" t="s">
+      <c r="G49" t="s">
         <v>518</v>
       </c>
-      <c r="H49" s="15" t="s">
+      <c r="H49" t="s">
         <v>519</v>
       </c>
-      <c r="I49" s="15" t="s">
+      <c r="I49" t="s">
         <v>520</v>
       </c>
-      <c r="J49" s="15" t="s">
+      <c r="J49" t="s">
         <v>521</v>
       </c>
-      <c r="K49" s="16">
+      <c r="K49" s="12">
         <v>44631</v>
       </c>
-      <c r="L49" s="15" t="s">
+      <c r="L49" t="s">
         <v>522</v>
       </c>
     </row>
@@ -5970,37 +8136,37 @@
       <c r="A50">
         <v>49</v>
       </c>
-      <c r="B50" s="15" t="s">
+      <c r="B50" t="s">
         <v>523</v>
       </c>
-      <c r="C50" s="15" t="s">
+      <c r="C50" t="s">
         <v>524</v>
       </c>
-      <c r="D50" s="15" t="s">
+      <c r="D50" t="s">
         <v>525</v>
       </c>
-      <c r="E50" s="15" t="s">
+      <c r="E50" t="s">
         <v>526</v>
       </c>
-      <c r="F50" s="15" t="s">
+      <c r="F50" t="s">
         <v>527</v>
       </c>
-      <c r="G50" s="15" t="s">
+      <c r="G50" t="s">
         <v>528</v>
       </c>
-      <c r="H50" s="15" t="s">
+      <c r="H50" t="s">
         <v>529</v>
       </c>
-      <c r="I50" s="15" t="s">
+      <c r="I50" t="s">
         <v>530</v>
       </c>
-      <c r="J50" s="15" t="s">
+      <c r="J50" t="s">
         <v>531</v>
       </c>
-      <c r="K50" s="16">
+      <c r="K50" s="12">
         <v>44630</v>
       </c>
-      <c r="L50" s="15" t="s">
+      <c r="L50" t="s">
         <v>532</v>
       </c>
     </row>
@@ -6008,37 +8174,37 @@
       <c r="A51">
         <v>50</v>
       </c>
-      <c r="B51" s="15" t="s">
+      <c r="B51" t="s">
         <v>533</v>
       </c>
-      <c r="C51" s="15" t="s">
+      <c r="C51" t="s">
         <v>534</v>
       </c>
-      <c r="D51" s="15" t="s">
+      <c r="D51" t="s">
         <v>535</v>
       </c>
-      <c r="E51" s="15" t="s">
+      <c r="E51" t="s">
         <v>536</v>
       </c>
-      <c r="F51" s="15" t="s">
+      <c r="F51" t="s">
         <v>537</v>
       </c>
-      <c r="G51" s="15" t="s">
+      <c r="G51" t="s">
         <v>311</v>
       </c>
-      <c r="H51" s="15" t="s">
+      <c r="H51" t="s">
         <v>538</v>
       </c>
-      <c r="I51" s="15" t="s">
+      <c r="I51" t="s">
         <v>539</v>
       </c>
-      <c r="J51" s="15" t="s">
+      <c r="J51" t="s">
         <v>540</v>
       </c>
-      <c r="K51" s="16">
+      <c r="K51" s="12">
         <v>44532</v>
       </c>
-      <c r="L51" s="15" t="s">
+      <c r="L51" t="s">
         <v>541</v>
       </c>
     </row>
@@ -6046,37 +8212,37 @@
       <c r="A52">
         <v>51</v>
       </c>
-      <c r="B52" s="15" t="s">
+      <c r="B52" t="s">
         <v>542</v>
       </c>
-      <c r="C52" s="15" t="s">
+      <c r="C52" t="s">
         <v>543</v>
       </c>
-      <c r="D52" s="15" t="s">
+      <c r="D52" t="s">
         <v>544</v>
       </c>
-      <c r="E52" s="15" t="s">
+      <c r="E52" t="s">
         <v>545</v>
       </c>
-      <c r="F52" s="15" t="s">
+      <c r="F52" t="s">
         <v>546</v>
       </c>
-      <c r="G52" s="15" t="s">
+      <c r="G52" t="s">
         <v>547</v>
       </c>
-      <c r="H52" s="15" t="s">
+      <c r="H52" t="s">
         <v>548</v>
       </c>
-      <c r="I52" s="15" t="s">
+      <c r="I52" t="s">
         <v>549</v>
       </c>
-      <c r="J52" s="15" t="s">
+      <c r="J52" t="s">
         <v>550</v>
       </c>
-      <c r="K52" s="16">
+      <c r="K52" s="12">
         <v>44274</v>
       </c>
-      <c r="L52" s="15" t="s">
+      <c r="L52" t="s">
         <v>551</v>
       </c>
     </row>
@@ -6084,37 +8250,37 @@
       <c r="A53">
         <v>52</v>
       </c>
-      <c r="B53" s="15" t="s">
+      <c r="B53" t="s">
         <v>552</v>
       </c>
-      <c r="C53" s="15" t="s">
+      <c r="C53" t="s">
         <v>553</v>
       </c>
-      <c r="D53" s="15" t="s">
+      <c r="D53" t="s">
         <v>554</v>
       </c>
-      <c r="E53" s="15" t="s">
+      <c r="E53" t="s">
         <v>555</v>
       </c>
-      <c r="F53" s="15" t="s">
+      <c r="F53" t="s">
         <v>556</v>
       </c>
-      <c r="G53" s="15" t="s">
+      <c r="G53" t="s">
         <v>557</v>
       </c>
-      <c r="H53" s="15" t="s">
+      <c r="H53" t="s">
         <v>558</v>
       </c>
-      <c r="I53" s="15" t="s">
+      <c r="I53" t="s">
         <v>559</v>
       </c>
-      <c r="J53" s="15" t="s">
+      <c r="J53" t="s">
         <v>560</v>
       </c>
-      <c r="K53" s="16">
+      <c r="K53" s="12">
         <v>44282</v>
       </c>
-      <c r="L53" s="15" t="s">
+      <c r="L53" t="s">
         <v>561</v>
       </c>
     </row>
@@ -6122,37 +8288,37 @@
       <c r="A54">
         <v>53</v>
       </c>
-      <c r="B54" s="15" t="s">
+      <c r="B54" t="s">
         <v>562</v>
       </c>
-      <c r="C54" s="15" t="s">
+      <c r="C54" t="s">
         <v>563</v>
       </c>
-      <c r="D54" s="15" t="s">
+      <c r="D54" t="s">
         <v>564</v>
       </c>
-      <c r="E54" s="15" t="s">
+      <c r="E54" t="s">
         <v>565</v>
       </c>
-      <c r="F54" s="15" t="s">
+      <c r="F54" t="s">
         <v>566</v>
       </c>
-      <c r="G54" s="15" t="s">
+      <c r="G54" t="s">
         <v>567</v>
       </c>
-      <c r="H54" s="15" t="s">
+      <c r="H54" t="s">
         <v>568</v>
       </c>
-      <c r="I54" s="15" t="s">
+      <c r="I54" t="s">
         <v>569</v>
       </c>
-      <c r="J54" s="15" t="s">
+      <c r="J54" t="s">
         <v>570</v>
       </c>
-      <c r="K54" s="16">
+      <c r="K54" s="12">
         <v>44263</v>
       </c>
-      <c r="L54" s="15" t="s">
+      <c r="L54" t="s">
         <v>571</v>
       </c>
     </row>
@@ -6160,37 +8326,37 @@
       <c r="A55">
         <v>54</v>
       </c>
-      <c r="B55" s="15" t="s">
+      <c r="B55" t="s">
         <v>572</v>
       </c>
-      <c r="C55" s="15" t="s">
+      <c r="C55" t="s">
         <v>573</v>
       </c>
-      <c r="D55" s="15" t="s">
+      <c r="D55" t="s">
         <v>574</v>
       </c>
-      <c r="E55" s="15" t="s">
+      <c r="E55" t="s">
         <v>575</v>
       </c>
-      <c r="F55" s="15" t="s">
+      <c r="F55" t="s">
         <v>576</v>
       </c>
-      <c r="G55" s="15" t="s">
+      <c r="G55" t="s">
         <v>577</v>
       </c>
-      <c r="H55" s="15" t="s">
+      <c r="H55" t="s">
         <v>578</v>
       </c>
-      <c r="I55" s="15" t="s">
+      <c r="I55" t="s">
         <v>579</v>
       </c>
-      <c r="J55" s="15" t="s">
+      <c r="J55" t="s">
         <v>580</v>
       </c>
-      <c r="K55" s="16">
+      <c r="K55" s="12">
         <v>44119</v>
       </c>
-      <c r="L55" s="15" t="s">
+      <c r="L55" t="s">
         <v>581</v>
       </c>
     </row>
@@ -6198,37 +8364,37 @@
       <c r="A56">
         <v>55</v>
       </c>
-      <c r="B56" s="15" t="s">
+      <c r="B56" t="s">
         <v>582</v>
       </c>
-      <c r="C56" s="15" t="s">
+      <c r="C56" t="s">
         <v>583</v>
       </c>
-      <c r="D56" s="15" t="s">
+      <c r="D56" t="s">
         <v>584</v>
       </c>
-      <c r="E56" s="15" t="s">
+      <c r="E56" t="s">
         <v>585</v>
       </c>
-      <c r="F56" s="15" t="s">
+      <c r="F56" t="s">
         <v>586</v>
       </c>
-      <c r="G56" s="15" t="s">
+      <c r="G56" t="s">
         <v>587</v>
       </c>
-      <c r="H56" s="15" t="s">
+      <c r="H56" t="s">
         <v>588</v>
       </c>
-      <c r="I56" s="15" t="s">
+      <c r="I56" t="s">
         <v>589</v>
       </c>
-      <c r="J56" s="15" t="s">
+      <c r="J56" t="s">
         <v>590</v>
       </c>
-      <c r="K56" s="16">
+      <c r="K56" s="12">
         <v>44574</v>
       </c>
-      <c r="L56" s="15" t="s">
+      <c r="L56" t="s">
         <v>591</v>
       </c>
     </row>
@@ -6236,37 +8402,37 @@
       <c r="A57">
         <v>56</v>
       </c>
-      <c r="B57" s="15" t="s">
+      <c r="B57" t="s">
         <v>592</v>
       </c>
-      <c r="C57" s="15" t="s">
+      <c r="C57" t="s">
         <v>593</v>
       </c>
-      <c r="D57" s="15" t="s">
+      <c r="D57" t="s">
         <v>594</v>
       </c>
-      <c r="E57" s="15" t="s">
+      <c r="E57" t="s">
         <v>595</v>
       </c>
-      <c r="F57" s="15" t="s">
+      <c r="F57" t="s">
         <v>596</v>
       </c>
-      <c r="G57" s="15" t="s">
+      <c r="G57" t="s">
         <v>597</v>
       </c>
-      <c r="H57" s="15" t="s">
+      <c r="H57" t="s">
         <v>598</v>
       </c>
-      <c r="I57" s="15" t="s">
+      <c r="I57" t="s">
         <v>599</v>
       </c>
-      <c r="J57" s="15" t="s">
+      <c r="J57" t="s">
         <v>600</v>
       </c>
-      <c r="K57" s="16">
+      <c r="K57" s="12">
         <v>43976</v>
       </c>
-      <c r="L57" s="15" t="s">
+      <c r="L57" t="s">
         <v>601</v>
       </c>
     </row>
@@ -6274,37 +8440,37 @@
       <c r="A58">
         <v>57</v>
       </c>
-      <c r="B58" s="15" t="s">
+      <c r="B58" t="s">
         <v>602</v>
       </c>
-      <c r="C58" s="15" t="s">
+      <c r="C58" t="s">
         <v>603</v>
       </c>
-      <c r="D58" s="15" t="s">
+      <c r="D58" t="s">
         <v>604</v>
       </c>
-      <c r="E58" s="15" t="s">
+      <c r="E58" t="s">
         <v>605</v>
       </c>
-      <c r="F58" s="15" t="s">
+      <c r="F58" t="s">
         <v>606</v>
       </c>
-      <c r="G58" s="15" t="s">
+      <c r="G58" t="s">
         <v>607</v>
       </c>
-      <c r="H58" s="15" t="s">
+      <c r="H58" t="s">
         <v>608</v>
       </c>
-      <c r="I58" s="15" t="s">
+      <c r="I58" t="s">
         <v>609</v>
       </c>
-      <c r="J58" s="15" t="s">
+      <c r="J58" t="s">
         <v>610</v>
       </c>
-      <c r="K58" s="16">
+      <c r="K58" s="12">
         <v>44221</v>
       </c>
-      <c r="L58" s="15" t="s">
+      <c r="L58" t="s">
         <v>611</v>
       </c>
     </row>
@@ -6312,37 +8478,37 @@
       <c r="A59">
         <v>58</v>
       </c>
-      <c r="B59" s="15" t="s">
+      <c r="B59" t="s">
         <v>612</v>
       </c>
-      <c r="C59" s="15" t="s">
+      <c r="C59" t="s">
         <v>613</v>
       </c>
-      <c r="D59" s="15" t="s">
+      <c r="D59" t="s">
         <v>614</v>
       </c>
-      <c r="E59" s="15" t="s">
+      <c r="E59" t="s">
         <v>615</v>
       </c>
-      <c r="F59" s="15" t="s">
+      <c r="F59" t="s">
         <v>616</v>
       </c>
-      <c r="G59" s="15" t="s">
+      <c r="G59" t="s">
         <v>528</v>
       </c>
-      <c r="H59" s="15" t="s">
+      <c r="H59" t="s">
         <v>617</v>
       </c>
-      <c r="I59" s="15" t="s">
+      <c r="I59" t="s">
         <v>618</v>
       </c>
-      <c r="J59" s="15" t="s">
+      <c r="J59" t="s">
         <v>619</v>
       </c>
-      <c r="K59" s="16">
+      <c r="K59" s="12">
         <v>44272</v>
       </c>
-      <c r="L59" s="15" t="s">
+      <c r="L59" t="s">
         <v>620</v>
       </c>
     </row>
@@ -6350,37 +8516,37 @@
       <c r="A60">
         <v>59</v>
       </c>
-      <c r="B60" s="15" t="s">
+      <c r="B60" t="s">
         <v>621</v>
       </c>
-      <c r="C60" s="15" t="s">
+      <c r="C60" t="s">
         <v>622</v>
       </c>
-      <c r="D60" s="15" t="s">
+      <c r="D60" t="s">
         <v>623</v>
       </c>
-      <c r="E60" s="15" t="s">
+      <c r="E60" t="s">
         <v>624</v>
       </c>
-      <c r="F60" s="15" t="s">
+      <c r="F60" t="s">
         <v>625</v>
       </c>
-      <c r="G60" s="15" t="s">
+      <c r="G60" t="s">
         <v>232</v>
       </c>
-      <c r="H60" s="15" t="s">
+      <c r="H60" t="s">
         <v>626</v>
       </c>
-      <c r="I60" s="15" t="s">
+      <c r="I60" t="s">
         <v>627</v>
       </c>
-      <c r="J60" s="15" t="s">
+      <c r="J60" t="s">
         <v>628</v>
       </c>
-      <c r="K60" s="16">
+      <c r="K60" s="12">
         <v>44150</v>
       </c>
-      <c r="L60" s="15" t="s">
+      <c r="L60" t="s">
         <v>629</v>
       </c>
     </row>
@@ -6388,37 +8554,37 @@
       <c r="A61">
         <v>60</v>
       </c>
-      <c r="B61" s="15" t="s">
+      <c r="B61" t="s">
         <v>630</v>
       </c>
-      <c r="C61" s="15" t="s">
+      <c r="C61" t="s">
         <v>631</v>
       </c>
-      <c r="D61" s="15" t="s">
+      <c r="D61" t="s">
         <v>632</v>
       </c>
-      <c r="E61" s="15" t="s">
+      <c r="E61" t="s">
         <v>633</v>
       </c>
-      <c r="F61" s="15" t="s">
+      <c r="F61" t="s">
         <v>634</v>
       </c>
-      <c r="G61" s="15" t="s">
+      <c r="G61" t="s">
         <v>635</v>
       </c>
-      <c r="H61" s="15" t="s">
+      <c r="H61" t="s">
         <v>636</v>
       </c>
-      <c r="I61" s="15" t="s">
+      <c r="I61" t="s">
         <v>637</v>
       </c>
-      <c r="J61" s="15" t="s">
+      <c r="J61" t="s">
         <v>638</v>
       </c>
-      <c r="K61" s="16">
+      <c r="K61" s="12">
         <v>44185</v>
       </c>
-      <c r="L61" s="15" t="s">
+      <c r="L61" t="s">
         <v>639</v>
       </c>
     </row>
@@ -6426,37 +8592,37 @@
       <c r="A62">
         <v>61</v>
       </c>
-      <c r="B62" s="15" t="s">
+      <c r="B62" t="s">
         <v>640</v>
       </c>
-      <c r="C62" s="15" t="s">
+      <c r="C62" t="s">
         <v>641</v>
       </c>
-      <c r="D62" s="15" t="s">
+      <c r="D62" t="s">
         <v>642</v>
       </c>
-      <c r="E62" s="15" t="s">
+      <c r="E62" t="s">
         <v>643</v>
       </c>
-      <c r="F62" s="15" t="s">
+      <c r="F62" t="s">
         <v>644</v>
       </c>
-      <c r="G62" s="15" t="s">
+      <c r="G62" t="s">
         <v>645</v>
       </c>
-      <c r="H62" s="15" t="s">
+      <c r="H62" t="s">
         <v>646</v>
       </c>
-      <c r="I62" s="15" t="s">
+      <c r="I62" t="s">
         <v>647</v>
       </c>
-      <c r="J62" s="15" t="s">
+      <c r="J62" t="s">
         <v>648</v>
       </c>
-      <c r="K62" s="16">
+      <c r="K62" s="12">
         <v>44064</v>
       </c>
-      <c r="L62" s="15" t="s">
+      <c r="L62" t="s">
         <v>649</v>
       </c>
     </row>
@@ -6464,37 +8630,37 @@
       <c r="A63">
         <v>62</v>
       </c>
-      <c r="B63" s="15" t="s">
+      <c r="B63" t="s">
         <v>650</v>
       </c>
-      <c r="C63" s="15" t="s">
+      <c r="C63" t="s">
         <v>651</v>
       </c>
-      <c r="D63" s="15" t="s">
+      <c r="D63" t="s">
         <v>652</v>
       </c>
-      <c r="E63" s="15" t="s">
+      <c r="E63" t="s">
         <v>653</v>
       </c>
-      <c r="F63" s="15" t="s">
+      <c r="F63" t="s">
         <v>654</v>
       </c>
-      <c r="G63" s="15" t="s">
+      <c r="G63" t="s">
         <v>173</v>
       </c>
-      <c r="H63" s="15" t="s">
+      <c r="H63" t="s">
         <v>655</v>
       </c>
-      <c r="I63" s="15" t="s">
+      <c r="I63" t="s">
         <v>656</v>
       </c>
-      <c r="J63" s="15" t="s">
+      <c r="J63" t="s">
         <v>657</v>
       </c>
-      <c r="K63" s="16">
+      <c r="K63" s="12">
         <v>44175</v>
       </c>
-      <c r="L63" s="15" t="s">
+      <c r="L63" t="s">
         <v>658</v>
       </c>
     </row>
@@ -6502,37 +8668,37 @@
       <c r="A64">
         <v>63</v>
       </c>
-      <c r="B64" s="15" t="s">
+      <c r="B64" t="s">
         <v>659</v>
       </c>
-      <c r="C64" s="15" t="s">
+      <c r="C64" t="s">
         <v>660</v>
       </c>
-      <c r="D64" s="15" t="s">
+      <c r="D64" t="s">
         <v>661</v>
       </c>
-      <c r="E64" s="15" t="s">
+      <c r="E64" t="s">
         <v>662</v>
       </c>
-      <c r="F64" s="15" t="s">
+      <c r="F64" t="s">
         <v>663</v>
       </c>
-      <c r="G64" s="15" t="s">
+      <c r="G64" t="s">
         <v>664</v>
       </c>
-      <c r="H64" s="15" t="s">
+      <c r="H64" t="s">
         <v>665</v>
       </c>
-      <c r="I64" s="15" t="s">
+      <c r="I64" t="s">
         <v>666</v>
       </c>
-      <c r="J64" s="15" t="s">
+      <c r="J64" t="s">
         <v>667</v>
       </c>
-      <c r="K64" s="16">
+      <c r="K64" s="12">
         <v>44644</v>
       </c>
-      <c r="L64" s="15" t="s">
+      <c r="L64" t="s">
         <v>668</v>
       </c>
     </row>
@@ -6540,37 +8706,37 @@
       <c r="A65">
         <v>64</v>
       </c>
-      <c r="B65" s="15" t="s">
+      <c r="B65" t="s">
         <v>669</v>
       </c>
-      <c r="C65" s="15" t="s">
+      <c r="C65" t="s">
         <v>670</v>
       </c>
-      <c r="D65" s="15" t="s">
+      <c r="D65" t="s">
         <v>671</v>
       </c>
-      <c r="E65" s="15" t="s">
+      <c r="E65" t="s">
         <v>230</v>
       </c>
-      <c r="F65" s="15" t="s">
+      <c r="F65" t="s">
         <v>672</v>
       </c>
-      <c r="G65" s="15" t="s">
+      <c r="G65" t="s">
         <v>261</v>
       </c>
-      <c r="H65" s="15" t="s">
+      <c r="H65" t="s">
         <v>673</v>
       </c>
-      <c r="I65" s="15" t="s">
+      <c r="I65" t="s">
         <v>674</v>
       </c>
-      <c r="J65" s="15" t="s">
+      <c r="J65" t="s">
         <v>675</v>
       </c>
-      <c r="K65" s="16">
+      <c r="K65" s="12">
         <v>44696</v>
       </c>
-      <c r="L65" s="15" t="s">
+      <c r="L65" t="s">
         <v>676</v>
       </c>
     </row>
@@ -6578,37 +8744,37 @@
       <c r="A66">
         <v>65</v>
       </c>
-      <c r="B66" s="15" t="s">
+      <c r="B66" t="s">
         <v>677</v>
       </c>
-      <c r="C66" s="15" t="s">
+      <c r="C66" t="s">
         <v>678</v>
       </c>
-      <c r="D66" s="15" t="s">
+      <c r="D66" t="s">
         <v>679</v>
       </c>
-      <c r="E66" s="15" t="s">
+      <c r="E66" t="s">
         <v>680</v>
       </c>
-      <c r="F66" s="15" t="s">
+      <c r="F66" t="s">
         <v>681</v>
       </c>
-      <c r="G66" s="15" t="s">
+      <c r="G66" t="s">
         <v>682</v>
       </c>
-      <c r="H66" s="15" t="s">
+      <c r="H66" t="s">
         <v>683</v>
       </c>
-      <c r="I66" s="15" t="s">
+      <c r="I66" t="s">
         <v>684</v>
       </c>
-      <c r="J66" s="15" t="s">
+      <c r="J66" t="s">
         <v>685</v>
       </c>
-      <c r="K66" s="16">
+      <c r="K66" s="12">
         <v>44198</v>
       </c>
-      <c r="L66" s="15" t="s">
+      <c r="L66" t="s">
         <v>686</v>
       </c>
     </row>
@@ -6616,37 +8782,37 @@
       <c r="A67">
         <v>66</v>
       </c>
-      <c r="B67" s="15" t="s">
+      <c r="B67" t="s">
         <v>687</v>
       </c>
-      <c r="C67" s="15" t="s">
+      <c r="C67" t="s">
         <v>688</v>
       </c>
-      <c r="D67" s="15" t="s">
+      <c r="D67" t="s">
         <v>689</v>
       </c>
-      <c r="E67" s="15" t="s">
+      <c r="E67" t="s">
         <v>690</v>
       </c>
-      <c r="F67" s="15" t="s">
+      <c r="F67" t="s">
         <v>691</v>
       </c>
-      <c r="G67" s="15" t="s">
+      <c r="G67" t="s">
         <v>692</v>
       </c>
-      <c r="H67" s="15" t="s">
+      <c r="H67" t="s">
         <v>693</v>
       </c>
-      <c r="I67" s="15" t="s">
+      <c r="I67" t="s">
         <v>694</v>
       </c>
-      <c r="J67" s="15" t="s">
+      <c r="J67" t="s">
         <v>695</v>
       </c>
-      <c r="K67" s="16">
+      <c r="K67" s="12">
         <v>44309</v>
       </c>
-      <c r="L67" s="15" t="s">
+      <c r="L67" t="s">
         <v>696</v>
       </c>
     </row>
@@ -6654,37 +8820,37 @@
       <c r="A68">
         <v>67</v>
       </c>
-      <c r="B68" s="15" t="s">
+      <c r="B68" t="s">
         <v>697</v>
       </c>
-      <c r="C68" s="15" t="s">
+      <c r="C68" t="s">
         <v>698</v>
       </c>
-      <c r="D68" s="15" t="s">
+      <c r="D68" t="s">
         <v>699</v>
       </c>
-      <c r="E68" s="15" t="s">
+      <c r="E68" t="s">
         <v>700</v>
       </c>
-      <c r="F68" s="15" t="s">
+      <c r="F68" t="s">
         <v>701</v>
       </c>
-      <c r="G68" s="15" t="s">
+      <c r="G68" t="s">
         <v>702</v>
       </c>
-      <c r="H68" s="15" t="s">
+      <c r="H68" t="s">
         <v>703</v>
       </c>
-      <c r="I68" s="15" t="s">
+      <c r="I68" t="s">
         <v>704</v>
       </c>
-      <c r="J68" s="15" t="s">
+      <c r="J68" t="s">
         <v>705</v>
       </c>
-      <c r="K68" s="16">
+      <c r="K68" s="12">
         <v>43850</v>
       </c>
-      <c r="L68" s="15" t="s">
+      <c r="L68" t="s">
         <v>706</v>
       </c>
     </row>
@@ -6692,37 +8858,37 @@
       <c r="A69">
         <v>68</v>
       </c>
-      <c r="B69" s="15" t="s">
+      <c r="B69" t="s">
         <v>707</v>
       </c>
-      <c r="C69" s="15" t="s">
+      <c r="C69" t="s">
         <v>357</v>
       </c>
-      <c r="D69" s="15" t="s">
+      <c r="D69" t="s">
         <v>708</v>
       </c>
-      <c r="E69" s="15" t="s">
+      <c r="E69" t="s">
         <v>709</v>
       </c>
-      <c r="F69" s="15" t="s">
+      <c r="F69" t="s">
         <v>710</v>
       </c>
-      <c r="G69" s="15" t="s">
+      <c r="G69" t="s">
         <v>711</v>
       </c>
-      <c r="H69" s="15" t="s">
+      <c r="H69" t="s">
         <v>712</v>
       </c>
-      <c r="I69" s="15" t="s">
+      <c r="I69" t="s">
         <v>713</v>
       </c>
-      <c r="J69" s="15" t="s">
+      <c r="J69" t="s">
         <v>714</v>
       </c>
-      <c r="K69" s="16">
+      <c r="K69" s="12">
         <v>44061</v>
       </c>
-      <c r="L69" s="15" t="s">
+      <c r="L69" t="s">
         <v>715</v>
       </c>
     </row>
@@ -6730,37 +8896,37 @@
       <c r="A70">
         <v>69</v>
       </c>
-      <c r="B70" s="15" t="s">
+      <c r="B70" t="s">
         <v>716</v>
       </c>
-      <c r="C70" s="15" t="s">
+      <c r="C70" t="s">
         <v>717</v>
       </c>
-      <c r="D70" s="15" t="s">
+      <c r="D70" t="s">
         <v>718</v>
       </c>
-      <c r="E70" s="15" t="s">
+      <c r="E70" t="s">
         <v>719</v>
       </c>
-      <c r="F70" s="15" t="s">
+      <c r="F70" t="s">
         <v>720</v>
       </c>
-      <c r="G70" s="15" t="s">
+      <c r="G70" t="s">
         <v>721</v>
       </c>
-      <c r="H70" s="15" t="s">
+      <c r="H70" t="s">
         <v>722</v>
       </c>
-      <c r="I70" s="15" t="s">
+      <c r="I70" t="s">
         <v>723</v>
       </c>
-      <c r="J70" s="15" t="s">
+      <c r="J70" t="s">
         <v>724</v>
       </c>
-      <c r="K70" s="16">
+      <c r="K70" s="12">
         <v>44227</v>
       </c>
-      <c r="L70" s="15" t="s">
+      <c r="L70" t="s">
         <v>725</v>
       </c>
     </row>
@@ -6768,37 +8934,37 @@
       <c r="A71">
         <v>70</v>
       </c>
-      <c r="B71" s="15" t="s">
+      <c r="B71" t="s">
         <v>726</v>
       </c>
-      <c r="C71" s="15" t="s">
+      <c r="C71" t="s">
         <v>727</v>
       </c>
-      <c r="D71" s="15" t="s">
+      <c r="D71" t="s">
         <v>728</v>
       </c>
-      <c r="E71" s="15" t="s">
+      <c r="E71" t="s">
         <v>729</v>
       </c>
-      <c r="F71" s="15" t="s">
+      <c r="F71" t="s">
         <v>730</v>
       </c>
-      <c r="G71" s="15" t="s">
+      <c r="G71" t="s">
         <v>547</v>
       </c>
-      <c r="H71" s="15" t="s">
+      <c r="H71" t="s">
         <v>731</v>
       </c>
-      <c r="I71" s="15" t="s">
+      <c r="I71" t="s">
         <v>732</v>
       </c>
-      <c r="J71" s="15" t="s">
+      <c r="J71" t="s">
         <v>733</v>
       </c>
-      <c r="K71" s="16">
+      <c r="K71" s="12">
         <v>43864</v>
       </c>
-      <c r="L71" s="15" t="s">
+      <c r="L71" t="s">
         <v>734</v>
       </c>
     </row>
@@ -6806,37 +8972,37 @@
       <c r="A72">
         <v>71</v>
       </c>
-      <c r="B72" s="15" t="s">
+      <c r="B72" t="s">
         <v>735</v>
       </c>
-      <c r="C72" s="15" t="s">
+      <c r="C72" t="s">
         <v>736</v>
       </c>
-      <c r="D72" s="15" t="s">
+      <c r="D72" t="s">
         <v>737</v>
       </c>
-      <c r="E72" s="15" t="s">
+      <c r="E72" t="s">
         <v>738</v>
       </c>
-      <c r="F72" s="15" t="s">
+      <c r="F72" t="s">
         <v>739</v>
       </c>
-      <c r="G72" s="15" t="s">
+      <c r="G72" t="s">
         <v>740</v>
       </c>
-      <c r="H72" s="15" t="s">
+      <c r="H72" t="s">
         <v>741</v>
       </c>
-      <c r="I72" s="15" t="s">
+      <c r="I72" t="s">
         <v>742</v>
       </c>
-      <c r="J72" s="15" t="s">
+      <c r="J72" t="s">
         <v>743</v>
       </c>
-      <c r="K72" s="16">
+      <c r="K72" s="12">
         <v>44247</v>
       </c>
-      <c r="L72" s="15" t="s">
+      <c r="L72" t="s">
         <v>744</v>
       </c>
     </row>
@@ -6844,37 +9010,37 @@
       <c r="A73">
         <v>72</v>
       </c>
-      <c r="B73" s="15" t="s">
+      <c r="B73" t="s">
         <v>745</v>
       </c>
-      <c r="C73" s="15" t="s">
+      <c r="C73" t="s">
         <v>574</v>
       </c>
-      <c r="D73" s="15" t="s">
+      <c r="D73" t="s">
         <v>746</v>
       </c>
-      <c r="E73" s="15" t="s">
+      <c r="E73" t="s">
         <v>747</v>
       </c>
-      <c r="F73" s="15" t="s">
+      <c r="F73" t="s">
         <v>748</v>
       </c>
-      <c r="G73" s="15" t="s">
+      <c r="G73" t="s">
         <v>749</v>
       </c>
-      <c r="H73" s="15" t="s">
+      <c r="H73" t="s">
         <v>750</v>
       </c>
-      <c r="I73" s="15" t="s">
+      <c r="I73" t="s">
         <v>751</v>
       </c>
-      <c r="J73" s="15" t="s">
+      <c r="J73" t="s">
         <v>752</v>
       </c>
-      <c r="K73" s="16">
+      <c r="K73" s="12">
         <v>43884</v>
       </c>
-      <c r="L73" s="15" t="s">
+      <c r="L73" t="s">
         <v>753</v>
       </c>
     </row>
@@ -6882,37 +9048,37 @@
       <c r="A74">
         <v>73</v>
       </c>
-      <c r="B74" s="15" t="s">
+      <c r="B74" t="s">
         <v>754</v>
       </c>
-      <c r="C74" s="15" t="s">
+      <c r="C74" t="s">
         <v>755</v>
       </c>
-      <c r="D74" s="15" t="s">
+      <c r="D74" t="s">
         <v>756</v>
       </c>
-      <c r="E74" s="15" t="s">
+      <c r="E74" t="s">
         <v>757</v>
       </c>
-      <c r="F74" s="15" t="s">
+      <c r="F74" t="s">
         <v>758</v>
       </c>
-      <c r="G74" s="15" t="s">
+      <c r="G74" t="s">
         <v>351</v>
       </c>
-      <c r="H74" s="15" t="s">
+      <c r="H74" t="s">
         <v>759</v>
       </c>
-      <c r="I74" s="15" t="s">
+      <c r="I74" t="s">
         <v>760</v>
       </c>
-      <c r="J74" s="15" t="s">
+      <c r="J74" t="s">
         <v>761</v>
       </c>
-      <c r="K74" s="16">
+      <c r="K74" s="12">
         <v>44065</v>
       </c>
-      <c r="L74" s="15" t="s">
+      <c r="L74" t="s">
         <v>762</v>
       </c>
     </row>
@@ -6920,37 +9086,37 @@
       <c r="A75">
         <v>74</v>
       </c>
-      <c r="B75" s="15" t="s">
+      <c r="B75" t="s">
         <v>763</v>
       </c>
-      <c r="C75" s="15" t="s">
+      <c r="C75" t="s">
         <v>764</v>
       </c>
-      <c r="D75" s="15" t="s">
+      <c r="D75" t="s">
         <v>765</v>
       </c>
-      <c r="E75" s="15" t="s">
+      <c r="E75" t="s">
         <v>766</v>
       </c>
-      <c r="F75" s="15" t="s">
+      <c r="F75" t="s">
         <v>767</v>
       </c>
-      <c r="G75" s="15" t="s">
+      <c r="G75" t="s">
         <v>768</v>
       </c>
-      <c r="H75" s="15" t="s">
+      <c r="H75" t="s">
         <v>769</v>
       </c>
-      <c r="I75" s="15" t="s">
+      <c r="I75" t="s">
         <v>770</v>
       </c>
-      <c r="J75" s="15" t="s">
+      <c r="J75" t="s">
         <v>771</v>
       </c>
-      <c r="K75" s="16">
+      <c r="K75" s="12">
         <v>43870</v>
       </c>
-      <c r="L75" s="15" t="s">
+      <c r="L75" t="s">
         <v>772</v>
       </c>
     </row>
@@ -6958,37 +9124,37 @@
       <c r="A76">
         <v>75</v>
       </c>
-      <c r="B76" s="15" t="s">
+      <c r="B76" t="s">
         <v>773</v>
       </c>
-      <c r="C76" s="15" t="s">
+      <c r="C76" t="s">
         <v>774</v>
       </c>
-      <c r="D76" s="15" t="s">
+      <c r="D76" t="s">
         <v>775</v>
       </c>
-      <c r="E76" s="15" t="s">
+      <c r="E76" t="s">
         <v>776</v>
       </c>
-      <c r="F76" s="15" t="s">
+      <c r="F76" t="s">
         <v>777</v>
       </c>
-      <c r="G76" s="15" t="s">
+      <c r="G76" t="s">
         <v>420</v>
       </c>
-      <c r="H76" s="15" t="s">
+      <c r="H76" t="s">
         <v>778</v>
       </c>
-      <c r="I76" s="15" t="s">
+      <c r="I76" t="s">
         <v>779</v>
       </c>
-      <c r="J76" s="15" t="s">
+      <c r="J76" t="s">
         <v>780</v>
       </c>
-      <c r="K76" s="16">
+      <c r="K76" s="12">
         <v>44576</v>
       </c>
-      <c r="L76" s="15" t="s">
+      <c r="L76" t="s">
         <v>781</v>
       </c>
     </row>
@@ -6996,37 +9162,37 @@
       <c r="A77">
         <v>76</v>
       </c>
-      <c r="B77" s="15" t="s">
+      <c r="B77" t="s">
         <v>782</v>
       </c>
-      <c r="C77" s="15" t="s">
+      <c r="C77" t="s">
         <v>783</v>
       </c>
-      <c r="D77" s="15" t="s">
+      <c r="D77" t="s">
         <v>784</v>
       </c>
-      <c r="E77" s="15" t="s">
+      <c r="E77" t="s">
         <v>785</v>
       </c>
-      <c r="F77" s="15" t="s">
+      <c r="F77" t="s">
         <v>786</v>
       </c>
-      <c r="G77" s="15" t="s">
+      <c r="G77" t="s">
         <v>787</v>
       </c>
-      <c r="H77" s="15" t="s">
+      <c r="H77" t="s">
         <v>788</v>
       </c>
-      <c r="I77" s="15" t="s">
+      <c r="I77" t="s">
         <v>789</v>
       </c>
-      <c r="J77" s="15" t="s">
+      <c r="J77" t="s">
         <v>790</v>
       </c>
-      <c r="K77" s="16">
+      <c r="K77" s="12">
         <v>44023</v>
       </c>
-      <c r="L77" s="15" t="s">
+      <c r="L77" t="s">
         <v>791</v>
       </c>
     </row>
@@ -7034,37 +9200,37 @@
       <c r="A78">
         <v>77</v>
       </c>
-      <c r="B78" s="15" t="s">
+      <c r="B78" t="s">
         <v>792</v>
       </c>
-      <c r="C78" s="15" t="s">
+      <c r="C78" t="s">
         <v>793</v>
       </c>
-      <c r="D78" s="15" t="s">
+      <c r="D78" t="s">
         <v>794</v>
       </c>
-      <c r="E78" s="15" t="s">
+      <c r="E78" t="s">
         <v>795</v>
       </c>
-      <c r="F78" s="15" t="s">
+      <c r="F78" t="s">
         <v>796</v>
       </c>
-      <c r="G78" s="15" t="s">
+      <c r="G78" t="s">
         <v>797</v>
       </c>
-      <c r="H78" s="15" t="s">
+      <c r="H78" t="s">
         <v>798</v>
       </c>
-      <c r="I78" s="15" t="s">
+      <c r="I78" t="s">
         <v>799</v>
       </c>
-      <c r="J78" s="15" t="s">
+      <c r="J78" t="s">
         <v>800</v>
       </c>
-      <c r="K78" s="16">
+      <c r="K78" s="12">
         <v>44401</v>
       </c>
-      <c r="L78" s="15" t="s">
+      <c r="L78" t="s">
         <v>801</v>
       </c>
     </row>
@@ -7072,37 +9238,37 @@
       <c r="A79">
         <v>78</v>
       </c>
-      <c r="B79" s="15" t="s">
+      <c r="B79" t="s">
         <v>802</v>
       </c>
-      <c r="C79" s="15" t="s">
+      <c r="C79" t="s">
         <v>803</v>
       </c>
-      <c r="D79" s="15" t="s">
+      <c r="D79" t="s">
         <v>804</v>
       </c>
-      <c r="E79" s="15" t="s">
+      <c r="E79" t="s">
         <v>805</v>
       </c>
-      <c r="F79" s="15" t="s">
+      <c r="F79" t="s">
         <v>806</v>
       </c>
-      <c r="G79" s="15" t="s">
+      <c r="G79" t="s">
         <v>807</v>
       </c>
-      <c r="H79" s="15" t="s">
+      <c r="H79" t="s">
         <v>808</v>
       </c>
-      <c r="I79" s="15" t="s">
+      <c r="I79" t="s">
         <v>809</v>
       </c>
-      <c r="J79" s="15" t="s">
+      <c r="J79" t="s">
         <v>810</v>
       </c>
-      <c r="K79" s="16">
+      <c r="K79" s="12">
         <v>44125</v>
       </c>
-      <c r="L79" s="15" t="s">
+      <c r="L79" t="s">
         <v>811</v>
       </c>
     </row>
@@ -7110,37 +9276,37 @@
       <c r="A80">
         <v>79</v>
       </c>
-      <c r="B80" s="15" t="s">
+      <c r="B80" t="s">
         <v>812</v>
       </c>
-      <c r="C80" s="15" t="s">
+      <c r="C80" t="s">
         <v>813</v>
       </c>
-      <c r="D80" s="15" t="s">
+      <c r="D80" t="s">
         <v>814</v>
       </c>
-      <c r="E80" s="15" t="s">
+      <c r="E80" t="s">
         <v>815</v>
       </c>
-      <c r="F80" s="15" t="s">
+      <c r="F80" t="s">
         <v>816</v>
       </c>
-      <c r="G80" s="15" t="s">
+      <c r="G80" t="s">
         <v>817</v>
       </c>
-      <c r="H80" s="15" t="s">
+      <c r="H80" t="s">
         <v>818</v>
       </c>
-      <c r="I80" s="15" t="s">
+      <c r="I80" t="s">
         <v>819</v>
       </c>
-      <c r="J80" s="15" t="s">
+      <c r="J80" t="s">
         <v>820</v>
       </c>
-      <c r="K80" s="16">
+      <c r="K80" s="12">
         <v>43990</v>
       </c>
-      <c r="L80" s="15" t="s">
+      <c r="L80" t="s">
         <v>821</v>
       </c>
     </row>
@@ -7148,37 +9314,37 @@
       <c r="A81">
         <v>80</v>
       </c>
-      <c r="B81" s="15" t="s">
+      <c r="B81" t="s">
         <v>822</v>
       </c>
-      <c r="C81" s="15" t="s">
+      <c r="C81" t="s">
         <v>823</v>
       </c>
-      <c r="D81" s="15" t="s">
+      <c r="D81" t="s">
         <v>824</v>
       </c>
-      <c r="E81" s="15" t="s">
+      <c r="E81" t="s">
         <v>825</v>
       </c>
-      <c r="F81" s="15" t="s">
+      <c r="F81" t="s">
         <v>826</v>
       </c>
-      <c r="G81" s="15" t="s">
+      <c r="G81" t="s">
         <v>827</v>
       </c>
-      <c r="H81" s="15" t="s">
+      <c r="H81" t="s">
         <v>828</v>
       </c>
-      <c r="I81" s="15" t="s">
+      <c r="I81" t="s">
         <v>829</v>
       </c>
-      <c r="J81" s="15" t="s">
+      <c r="J81" t="s">
         <v>830</v>
       </c>
-      <c r="K81" s="16">
+      <c r="K81" s="12">
         <v>44093</v>
       </c>
-      <c r="L81" s="15" t="s">
+      <c r="L81" t="s">
         <v>831</v>
       </c>
     </row>
@@ -7186,37 +9352,37 @@
       <c r="A82">
         <v>81</v>
       </c>
-      <c r="B82" s="15" t="s">
+      <c r="B82" t="s">
         <v>832</v>
       </c>
-      <c r="C82" s="15" t="s">
+      <c r="C82" t="s">
         <v>833</v>
       </c>
-      <c r="D82" s="15" t="s">
+      <c r="D82" t="s">
         <v>834</v>
       </c>
-      <c r="E82" s="15" t="s">
+      <c r="E82" t="s">
         <v>835</v>
       </c>
-      <c r="F82" s="15" t="s">
+      <c r="F82" t="s">
         <v>836</v>
       </c>
-      <c r="G82" s="15" t="s">
+      <c r="G82" t="s">
         <v>837</v>
       </c>
-      <c r="H82" s="15" t="s">
+      <c r="H82" t="s">
         <v>838</v>
       </c>
-      <c r="I82" s="15" t="s">
+      <c r="I82" t="s">
         <v>839</v>
       </c>
-      <c r="J82" s="15" t="s">
+      <c r="J82" t="s">
         <v>840</v>
       </c>
-      <c r="K82" s="16">
+      <c r="K82" s="12">
         <v>44513</v>
       </c>
-      <c r="L82" s="15" t="s">
+      <c r="L82" t="s">
         <v>841</v>
       </c>
     </row>
@@ -7224,37 +9390,37 @@
       <c r="A83">
         <v>82</v>
       </c>
-      <c r="B83" s="15" t="s">
+      <c r="B83" t="s">
         <v>842</v>
       </c>
-      <c r="C83" s="15" t="s">
+      <c r="C83" t="s">
         <v>843</v>
       </c>
-      <c r="D83" s="15" t="s">
+      <c r="D83" t="s">
         <v>844</v>
       </c>
-      <c r="E83" s="15" t="s">
+      <c r="E83" t="s">
         <v>845</v>
       </c>
-      <c r="F83" s="15" t="s">
+      <c r="F83" t="s">
         <v>846</v>
       </c>
-      <c r="G83" s="15" t="s">
+      <c r="G83" t="s">
         <v>331</v>
       </c>
-      <c r="H83" s="15" t="s">
+      <c r="H83" t="s">
         <v>847</v>
       </c>
-      <c r="I83" s="15" t="s">
+      <c r="I83" t="s">
         <v>848</v>
       </c>
-      <c r="J83" s="15" t="s">
+      <c r="J83" t="s">
         <v>849</v>
       </c>
-      <c r="K83" s="16">
+      <c r="K83" s="12">
         <v>44451</v>
       </c>
-      <c r="L83" s="15" t="s">
+      <c r="L83" t="s">
         <v>850</v>
       </c>
     </row>
@@ -7262,37 +9428,37 @@
       <c r="A84">
         <v>83</v>
       </c>
-      <c r="B84" s="15" t="s">
+      <c r="B84" t="s">
         <v>851</v>
       </c>
-      <c r="C84" s="15" t="s">
+      <c r="C84" t="s">
         <v>852</v>
       </c>
-      <c r="D84" s="15" t="s">
+      <c r="D84" t="s">
         <v>853</v>
       </c>
-      <c r="E84" s="15" t="s">
+      <c r="E84" t="s">
         <v>854</v>
       </c>
-      <c r="F84" s="15" t="s">
+      <c r="F84" t="s">
         <v>855</v>
       </c>
-      <c r="G84" s="15" t="s">
+      <c r="G84" t="s">
         <v>856</v>
       </c>
-      <c r="H84" s="15" t="s">
+      <c r="H84" t="s">
         <v>857</v>
       </c>
-      <c r="I84" s="15" t="s">
+      <c r="I84" t="s">
         <v>858</v>
       </c>
-      <c r="J84" s="15" t="s">
+      <c r="J84" t="s">
         <v>859</v>
       </c>
-      <c r="K84" s="16">
+      <c r="K84" s="12">
         <v>44193</v>
       </c>
-      <c r="L84" s="15" t="s">
+      <c r="L84" t="s">
         <v>860</v>
       </c>
     </row>
@@ -7300,37 +9466,37 @@
       <c r="A85">
         <v>84</v>
       </c>
-      <c r="B85" s="15" t="s">
+      <c r="B85" t="s">
         <v>861</v>
       </c>
-      <c r="C85" s="15" t="s">
+      <c r="C85" t="s">
         <v>862</v>
       </c>
-      <c r="D85" s="15" t="s">
+      <c r="D85" t="s">
         <v>863</v>
       </c>
-      <c r="E85" s="15" t="s">
+      <c r="E85" t="s">
         <v>864</v>
       </c>
-      <c r="F85" s="15" t="s">
+      <c r="F85" t="s">
         <v>865</v>
       </c>
-      <c r="G85" s="15" t="s">
+      <c r="G85" t="s">
         <v>203</v>
       </c>
-      <c r="H85" s="15" t="s">
+      <c r="H85" t="s">
         <v>866</v>
       </c>
-      <c r="I85" s="15" t="s">
+      <c r="I85" t="s">
         <v>867</v>
       </c>
-      <c r="J85" s="15" t="s">
+      <c r="J85" t="s">
         <v>868</v>
       </c>
-      <c r="K85" s="16">
+      <c r="K85" s="12">
         <v>44515</v>
       </c>
-      <c r="L85" s="15" t="s">
+      <c r="L85" t="s">
         <v>869</v>
       </c>
     </row>
@@ -7338,37 +9504,37 @@
       <c r="A86">
         <v>85</v>
       </c>
-      <c r="B86" s="15" t="s">
+      <c r="B86" t="s">
         <v>870</v>
       </c>
-      <c r="C86" s="15" t="s">
+      <c r="C86" t="s">
         <v>871</v>
       </c>
-      <c r="D86" s="15" t="s">
+      <c r="D86" t="s">
         <v>872</v>
       </c>
-      <c r="E86" s="15" t="s">
+      <c r="E86" t="s">
         <v>873</v>
       </c>
-      <c r="F86" s="15" t="s">
+      <c r="F86" t="s">
         <v>874</v>
       </c>
-      <c r="G86" s="15" t="s">
+      <c r="G86" t="s">
         <v>875</v>
       </c>
-      <c r="H86" s="15" t="s">
+      <c r="H86" t="s">
         <v>876</v>
       </c>
-      <c r="I86" s="15" t="s">
+      <c r="I86" t="s">
         <v>877</v>
       </c>
-      <c r="J86" s="15" t="s">
+      <c r="J86" t="s">
         <v>878</v>
       </c>
-      <c r="K86" s="16">
+      <c r="K86" s="12">
         <v>43879</v>
       </c>
-      <c r="L86" s="15" t="s">
+      <c r="L86" t="s">
         <v>879</v>
       </c>
     </row>
@@ -7376,37 +9542,37 @@
       <c r="A87">
         <v>86</v>
       </c>
-      <c r="B87" s="15" t="s">
+      <c r="B87" t="s">
         <v>880</v>
       </c>
-      <c r="C87" s="15" t="s">
+      <c r="C87" t="s">
         <v>881</v>
       </c>
-      <c r="D87" s="15" t="s">
+      <c r="D87" t="s">
         <v>882</v>
       </c>
-      <c r="E87" s="15" t="s">
+      <c r="E87" t="s">
         <v>883</v>
       </c>
-      <c r="F87" s="15" t="s">
+      <c r="F87" t="s">
         <v>884</v>
       </c>
-      <c r="G87" s="15" t="s">
+      <c r="G87" t="s">
         <v>885</v>
       </c>
-      <c r="H87" s="15" t="s">
+      <c r="H87" t="s">
         <v>886</v>
       </c>
-      <c r="I87" s="15" t="s">
+      <c r="I87" t="s">
         <v>887</v>
       </c>
-      <c r="J87" s="15" t="s">
+      <c r="J87" t="s">
         <v>888</v>
       </c>
-      <c r="K87" s="16">
+      <c r="K87" s="12">
         <v>44694</v>
       </c>
-      <c r="L87" s="15" t="s">
+      <c r="L87" t="s">
         <v>889</v>
       </c>
     </row>
@@ -7414,37 +9580,37 @@
       <c r="A88">
         <v>87</v>
       </c>
-      <c r="B88" s="15" t="s">
+      <c r="B88" t="s">
         <v>890</v>
       </c>
-      <c r="C88" s="15" t="s">
+      <c r="C88" t="s">
         <v>891</v>
       </c>
-      <c r="D88" s="15" t="s">
+      <c r="D88" t="s">
         <v>892</v>
       </c>
-      <c r="E88" s="15" t="s">
+      <c r="E88" t="s">
         <v>893</v>
       </c>
-      <c r="F88" s="15" t="s">
+      <c r="F88" t="s">
         <v>894</v>
       </c>
-      <c r="G88" s="15" t="s">
+      <c r="G88" t="s">
         <v>895</v>
       </c>
-      <c r="H88" s="15" t="s">
+      <c r="H88" t="s">
         <v>896</v>
       </c>
-      <c r="I88" s="15" t="s">
+      <c r="I88" t="s">
         <v>897</v>
       </c>
-      <c r="J88" s="15" t="s">
+      <c r="J88" t="s">
         <v>898</v>
       </c>
-      <c r="K88" s="16">
+      <c r="K88" s="12">
         <v>44033</v>
       </c>
-      <c r="L88" s="15" t="s">
+      <c r="L88" t="s">
         <v>899</v>
       </c>
     </row>
@@ -7452,37 +9618,37 @@
       <c r="A89">
         <v>88</v>
       </c>
-      <c r="B89" s="15" t="s">
+      <c r="B89" t="s">
         <v>900</v>
       </c>
-      <c r="C89" s="15" t="s">
+      <c r="C89" t="s">
         <v>901</v>
       </c>
-      <c r="D89" s="15" t="s">
+      <c r="D89" t="s">
         <v>902</v>
       </c>
-      <c r="E89" s="15" t="s">
+      <c r="E89" t="s">
         <v>903</v>
       </c>
-      <c r="F89" s="15" t="s">
+      <c r="F89" t="s">
         <v>904</v>
       </c>
-      <c r="G89" s="15" t="s">
+      <c r="G89" t="s">
         <v>905</v>
       </c>
-      <c r="H89" s="15" t="s">
+      <c r="H89" t="s">
         <v>906</v>
       </c>
-      <c r="I89" s="15" t="s">
+      <c r="I89" t="s">
         <v>907</v>
       </c>
-      <c r="J89" s="15" t="s">
+      <c r="J89" t="s">
         <v>908</v>
       </c>
-      <c r="K89" s="16">
+      <c r="K89" s="12">
         <v>44145</v>
       </c>
-      <c r="L89" s="15" t="s">
+      <c r="L89" t="s">
         <v>909</v>
       </c>
     </row>
@@ -7490,37 +9656,37 @@
       <c r="A90">
         <v>89</v>
       </c>
-      <c r="B90" s="15" t="s">
+      <c r="B90" t="s">
         <v>910</v>
       </c>
-      <c r="C90" s="15" t="s">
+      <c r="C90" t="s">
         <v>911</v>
       </c>
-      <c r="D90" s="15" t="s">
+      <c r="D90" t="s">
         <v>912</v>
       </c>
-      <c r="E90" s="15" t="s">
+      <c r="E90" t="s">
         <v>913</v>
       </c>
-      <c r="F90" s="15" t="s">
+      <c r="F90" t="s">
         <v>914</v>
       </c>
-      <c r="G90" s="15" t="s">
+      <c r="G90" t="s">
         <v>915</v>
       </c>
-      <c r="H90" s="15" t="s">
+      <c r="H90" t="s">
         <v>916</v>
       </c>
-      <c r="I90" s="15" t="s">
+      <c r="I90" t="s">
         <v>917</v>
       </c>
-      <c r="J90" s="15" t="s">
+      <c r="J90" t="s">
         <v>918</v>
       </c>
-      <c r="K90" s="16">
+      <c r="K90" s="12">
         <v>44301</v>
       </c>
-      <c r="L90" s="15" t="s">
+      <c r="L90" t="s">
         <v>919</v>
       </c>
     </row>
@@ -7528,37 +9694,37 @@
       <c r="A91">
         <v>90</v>
       </c>
-      <c r="B91" s="15" t="s">
+      <c r="B91" t="s">
         <v>920</v>
       </c>
-      <c r="C91" s="15" t="s">
+      <c r="C91" t="s">
         <v>921</v>
       </c>
-      <c r="D91" s="15" t="s">
+      <c r="D91" t="s">
         <v>922</v>
       </c>
-      <c r="E91" s="15" t="s">
+      <c r="E91" t="s">
         <v>923</v>
       </c>
-      <c r="F91" s="15" t="s">
+      <c r="F91" t="s">
         <v>924</v>
       </c>
-      <c r="G91" s="15" t="s">
+      <c r="G91" t="s">
         <v>925</v>
       </c>
-      <c r="H91" s="15" t="s">
+      <c r="H91" t="s">
         <v>926</v>
       </c>
-      <c r="I91" s="15" t="s">
+      <c r="I91" t="s">
         <v>927</v>
       </c>
-      <c r="J91" s="15" t="s">
+      <c r="J91" t="s">
         <v>928</v>
       </c>
-      <c r="K91" s="16">
+      <c r="K91" s="12">
         <v>44205</v>
       </c>
-      <c r="L91" s="15" t="s">
+      <c r="L91" t="s">
         <v>929</v>
       </c>
     </row>
@@ -7566,37 +9732,37 @@
       <c r="A92">
         <v>91</v>
       </c>
-      <c r="B92" s="15" t="s">
+      <c r="B92" t="s">
         <v>930</v>
       </c>
-      <c r="C92" s="15" t="s">
+      <c r="C92" t="s">
         <v>931</v>
       </c>
-      <c r="D92" s="15" t="s">
+      <c r="D92" t="s">
         <v>932</v>
       </c>
-      <c r="E92" s="15" t="s">
+      <c r="E92" t="s">
         <v>933</v>
       </c>
-      <c r="F92" s="15" t="s">
+      <c r="F92" t="s">
         <v>934</v>
       </c>
-      <c r="G92" s="15" t="s">
+      <c r="G92" t="s">
         <v>935</v>
       </c>
-      <c r="H92" s="15" t="s">
+      <c r="H92" t="s">
         <v>936</v>
       </c>
-      <c r="I92" s="15" t="s">
+      <c r="I92" t="s">
         <v>937</v>
       </c>
-      <c r="J92" s="15" t="s">
+      <c r="J92" t="s">
         <v>938</v>
       </c>
-      <c r="K92" s="16">
+      <c r="K92" s="12">
         <v>43916</v>
       </c>
-      <c r="L92" s="15" t="s">
+      <c r="L92" t="s">
         <v>939</v>
       </c>
     </row>
@@ -7604,37 +9770,37 @@
       <c r="A93">
         <v>92</v>
       </c>
-      <c r="B93" s="15" t="s">
+      <c r="B93" t="s">
         <v>940</v>
       </c>
-      <c r="C93" s="15" t="s">
+      <c r="C93" t="s">
         <v>287</v>
       </c>
-      <c r="D93" s="15" t="s">
+      <c r="D93" t="s">
         <v>210</v>
       </c>
-      <c r="E93" s="15" t="s">
+      <c r="E93" t="s">
         <v>941</v>
       </c>
-      <c r="F93" s="15" t="s">
+      <c r="F93" t="s">
         <v>942</v>
       </c>
-      <c r="G93" s="15" t="s">
+      <c r="G93" t="s">
         <v>943</v>
       </c>
-      <c r="H93" s="15" t="s">
+      <c r="H93" t="s">
         <v>944</v>
       </c>
-      <c r="I93" s="15" t="s">
+      <c r="I93" t="s">
         <v>945</v>
       </c>
-      <c r="J93" s="15" t="s">
+      <c r="J93" t="s">
         <v>946</v>
       </c>
-      <c r="K93" s="16">
+      <c r="K93" s="12">
         <v>44383</v>
       </c>
-      <c r="L93" s="15" t="s">
+      <c r="L93" t="s">
         <v>947</v>
       </c>
     </row>
@@ -7642,37 +9808,37 @@
       <c r="A94">
         <v>93</v>
       </c>
-      <c r="B94" s="15" t="s">
+      <c r="B94" t="s">
         <v>948</v>
       </c>
-      <c r="C94" s="15" t="s">
+      <c r="C94" t="s">
         <v>949</v>
       </c>
-      <c r="D94" s="15" t="s">
+      <c r="D94" t="s">
         <v>950</v>
       </c>
-      <c r="E94" s="15" t="s">
+      <c r="E94" t="s">
         <v>951</v>
       </c>
-      <c r="F94" s="15" t="s">
+      <c r="F94" t="s">
         <v>952</v>
       </c>
-      <c r="G94" s="15" t="s">
+      <c r="G94" t="s">
         <v>953</v>
       </c>
-      <c r="H94" s="15" t="s">
+      <c r="H94" t="s">
         <v>954</v>
       </c>
-      <c r="I94" s="15" t="s">
+      <c r="I94" t="s">
         <v>955</v>
       </c>
-      <c r="J94" s="15" t="s">
+      <c r="J94" t="s">
         <v>956</v>
       </c>
-      <c r="K94" s="16">
+      <c r="K94" s="12">
         <v>44376</v>
       </c>
-      <c r="L94" s="15" t="s">
+      <c r="L94" t="s">
         <v>957</v>
       </c>
     </row>
@@ -7680,37 +9846,37 @@
       <c r="A95">
         <v>94</v>
       </c>
-      <c r="B95" s="15" t="s">
+      <c r="B95" t="s">
         <v>958</v>
       </c>
-      <c r="C95" s="15" t="s">
+      <c r="C95" t="s">
         <v>436</v>
       </c>
-      <c r="D95" s="15" t="s">
+      <c r="D95" t="s">
         <v>959</v>
       </c>
-      <c r="E95" s="15" t="s">
+      <c r="E95" t="s">
         <v>960</v>
       </c>
-      <c r="F95" s="15" t="s">
+      <c r="F95" t="s">
         <v>961</v>
       </c>
-      <c r="G95" s="15" t="s">
+      <c r="G95" t="s">
         <v>420</v>
       </c>
-      <c r="H95" s="15" t="s">
+      <c r="H95" t="s">
         <v>962</v>
       </c>
-      <c r="I95" s="15" t="s">
+      <c r="I95" t="s">
         <v>963</v>
       </c>
-      <c r="J95" s="15" t="s">
+      <c r="J95" t="s">
         <v>964</v>
       </c>
-      <c r="K95" s="16">
+      <c r="K95" s="12">
         <v>44290</v>
       </c>
-      <c r="L95" s="15" t="s">
+      <c r="L95" t="s">
         <v>965</v>
       </c>
     </row>
@@ -7718,37 +9884,37 @@
       <c r="A96">
         <v>95</v>
       </c>
-      <c r="B96" s="15" t="s">
+      <c r="B96" t="s">
         <v>966</v>
       </c>
-      <c r="C96" s="15" t="s">
+      <c r="C96" t="s">
         <v>967</v>
       </c>
-      <c r="D96" s="15" t="s">
+      <c r="D96" t="s">
         <v>968</v>
       </c>
-      <c r="E96" s="15" t="s">
+      <c r="E96" t="s">
         <v>969</v>
       </c>
-      <c r="F96" s="15" t="s">
+      <c r="F96" t="s">
         <v>970</v>
       </c>
-      <c r="G96" s="15" t="s">
+      <c r="G96" t="s">
         <v>971</v>
       </c>
-      <c r="H96" s="15" t="s">
+      <c r="H96" t="s">
         <v>972</v>
       </c>
-      <c r="I96" s="15" t="s">
+      <c r="I96" t="s">
         <v>973</v>
       </c>
-      <c r="J96" s="15" t="s">
+      <c r="J96" t="s">
         <v>974</v>
       </c>
-      <c r="K96" s="16">
+      <c r="K96" s="12">
         <v>44609</v>
       </c>
-      <c r="L96" s="15" t="s">
+      <c r="L96" t="s">
         <v>975</v>
       </c>
     </row>
@@ -7756,37 +9922,37 @@
       <c r="A97">
         <v>96</v>
       </c>
-      <c r="B97" s="15" t="s">
+      <c r="B97" t="s">
         <v>976</v>
       </c>
-      <c r="C97" s="15" t="s">
+      <c r="C97" t="s">
         <v>977</v>
       </c>
-      <c r="D97" s="15" t="s">
+      <c r="D97" t="s">
         <v>476</v>
       </c>
-      <c r="E97" s="15" t="s">
+      <c r="E97" t="s">
         <v>978</v>
       </c>
-      <c r="F97" s="15" t="s">
+      <c r="F97" t="s">
         <v>979</v>
       </c>
-      <c r="G97" s="15" t="s">
+      <c r="G97" t="s">
         <v>980</v>
       </c>
-      <c r="H97" s="15" t="s">
+      <c r="H97" t="s">
         <v>981</v>
       </c>
-      <c r="I97" s="15" t="s">
+      <c r="I97" t="s">
         <v>982</v>
       </c>
-      <c r="J97" s="15" t="s">
+      <c r="J97" t="s">
         <v>983</v>
       </c>
-      <c r="K97" s="16">
+      <c r="K97" s="12">
         <v>44591</v>
       </c>
-      <c r="L97" s="15" t="s">
+      <c r="L97" t="s">
         <v>984</v>
       </c>
     </row>
@@ -7794,37 +9960,37 @@
       <c r="A98">
         <v>97</v>
       </c>
-      <c r="B98" s="15" t="s">
+      <c r="B98" t="s">
         <v>985</v>
       </c>
-      <c r="C98" s="15" t="s">
+      <c r="C98" t="s">
         <v>641</v>
       </c>
-      <c r="D98" s="15" t="s">
+      <c r="D98" t="s">
         <v>986</v>
       </c>
-      <c r="E98" s="15" t="s">
+      <c r="E98" t="s">
         <v>987</v>
       </c>
-      <c r="F98" s="15" t="s">
+      <c r="F98" t="s">
         <v>988</v>
       </c>
-      <c r="G98" s="15" t="s">
+      <c r="G98" t="s">
         <v>183</v>
       </c>
-      <c r="H98" s="15" t="s">
+      <c r="H98" t="s">
         <v>989</v>
       </c>
-      <c r="I98" s="15" t="s">
+      <c r="I98" t="s">
         <v>990</v>
       </c>
-      <c r="J98" s="15" t="s">
+      <c r="J98" t="s">
         <v>991</v>
       </c>
-      <c r="K98" s="16">
+      <c r="K98" s="12">
         <v>44387</v>
       </c>
-      <c r="L98" s="15" t="s">
+      <c r="L98" t="s">
         <v>992</v>
       </c>
     </row>
@@ -7832,37 +9998,37 @@
       <c r="A99">
         <v>98</v>
       </c>
-      <c r="B99" s="15" t="s">
+      <c r="B99" t="s">
         <v>993</v>
       </c>
-      <c r="C99" s="15" t="s">
+      <c r="C99" t="s">
         <v>994</v>
       </c>
-      <c r="D99" s="15" t="s">
+      <c r="D99" t="s">
         <v>995</v>
       </c>
-      <c r="E99" s="15" t="s">
+      <c r="E99" t="s">
         <v>996</v>
       </c>
-      <c r="F99" s="15" t="s">
+      <c r="F99" t="s">
         <v>997</v>
       </c>
-      <c r="G99" s="15" t="s">
+      <c r="G99" t="s">
         <v>420</v>
       </c>
-      <c r="H99" s="15" t="s">
+      <c r="H99" t="s">
         <v>998</v>
       </c>
-      <c r="I99" s="15" t="s">
+      <c r="I99" t="s">
         <v>999</v>
       </c>
-      <c r="J99" s="15" t="s">
+      <c r="J99" t="s">
         <v>1000</v>
       </c>
-      <c r="K99" s="16">
+      <c r="K99" s="12">
         <v>44457</v>
       </c>
-      <c r="L99" s="15" t="s">
+      <c r="L99" t="s">
         <v>1001</v>
       </c>
     </row>
@@ -7870,37 +10036,37 @@
       <c r="A100">
         <v>99</v>
       </c>
-      <c r="B100" s="15" t="s">
+      <c r="B100" t="s">
         <v>1002</v>
       </c>
-      <c r="C100" s="15" t="s">
+      <c r="C100" t="s">
         <v>1003</v>
       </c>
-      <c r="D100" s="15" t="s">
+      <c r="D100" t="s">
         <v>1004</v>
       </c>
-      <c r="E100" s="15" t="s">
+      <c r="E100" t="s">
         <v>1005</v>
       </c>
-      <c r="F100" s="15" t="s">
+      <c r="F100" t="s">
         <v>1006</v>
       </c>
-      <c r="G100" s="15" t="s">
+      <c r="G100" t="s">
         <v>1007</v>
       </c>
-      <c r="H100" s="15" t="s">
+      <c r="H100" t="s">
         <v>1008</v>
       </c>
-      <c r="I100" s="15" t="s">
+      <c r="I100" t="s">
         <v>1009</v>
       </c>
-      <c r="J100" s="15" t="s">
+      <c r="J100" t="s">
         <v>1010</v>
       </c>
-      <c r="K100" s="16">
+      <c r="K100" s="12">
         <v>44419</v>
       </c>
-      <c r="L100" s="15" t="s">
+      <c r="L100" t="s">
         <v>1011</v>
       </c>
     </row>
@@ -7908,37 +10074,37 @@
       <c r="A101">
         <v>100</v>
       </c>
-      <c r="B101" s="15" t="s">
+      <c r="B101" t="s">
         <v>1012</v>
       </c>
-      <c r="C101" s="15" t="s">
+      <c r="C101" t="s">
         <v>1013</v>
       </c>
-      <c r="D101" s="15" t="s">
+      <c r="D101" t="s">
         <v>1014</v>
       </c>
-      <c r="E101" s="15" t="s">
+      <c r="E101" t="s">
         <v>1015</v>
       </c>
-      <c r="F101" s="15" t="s">
+      <c r="F101" t="s">
         <v>1016</v>
       </c>
-      <c r="G101" s="15" t="s">
+      <c r="G101" t="s">
         <v>1017</v>
       </c>
-      <c r="H101" s="15" t="s">
+      <c r="H101" t="s">
         <v>1018</v>
       </c>
-      <c r="I101" s="15" t="s">
+      <c r="I101" t="s">
         <v>1019</v>
       </c>
-      <c r="J101" s="15" t="s">
+      <c r="J101" t="s">
         <v>1020</v>
       </c>
-      <c r="K101" s="16">
+      <c r="K101" s="12">
         <v>43901</v>
       </c>
-      <c r="L101" s="15" t="s">
+      <c r="L101" t="s">
         <v>1021</v>
       </c>
     </row>
@@ -7979,7 +10145,7 @@
       <c r="B2" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="10">
+      <c r="C2" s="6">
         <v>99</v>
       </c>
       <c r="D2" s="6">
@@ -7993,7 +10159,7 @@
       <c r="B3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="10">
+      <c r="C3" s="6">
         <v>86</v>
       </c>
       <c r="D3" s="6">
@@ -8007,7 +10173,7 @@
       <c r="B4" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4" s="6">
         <v>78</v>
       </c>
       <c r="D4" s="6">
@@ -8021,7 +10187,7 @@
       <c r="B5" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="6">
         <v>55</v>
       </c>
       <c r="D5" s="6">
@@ -8035,7 +10201,7 @@
       <c r="B6" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="6">
         <v>87</v>
       </c>
       <c r="D6" s="6">
@@ -8043,117 +10209,116 @@
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="15" t="s">
         <v>1022</v>
       </c>
-      <c r="C8" s="18"/>
+      <c r="C8" s="15"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="6" t="s">
         <v>1023</v>
       </c>
-      <c r="C10" s="19">
+      <c r="C10" s="6">
         <v>81</v>
       </c>
-      <c r="D10" s="17"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="6" t="s">
         <v>1024</v>
       </c>
-      <c r="C11" s="19">
+      <c r="C11" s="6">
         <v>7.3143694191638957</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="6" t="s">
         <v>1025</v>
       </c>
-      <c r="C12" s="19">
+      <c r="C12" s="6">
         <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="6" t="s">
         <v>1026</v>
       </c>
-      <c r="C13" s="19" t="e">
+      <c r="C13" s="6" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="6" t="s">
         <v>1027</v>
       </c>
-      <c r="C14" s="19">
+      <c r="C14" s="6">
         <v>16.355427233796124</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="6" t="s">
         <v>1028</v>
       </c>
-      <c r="C15" s="19">
+      <c r="C15" s="6">
         <v>267.5</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="6" t="s">
         <v>1029</v>
       </c>
-      <c r="C16" s="19">
+      <c r="C16" s="6">
         <v>1.8515852912918209</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B17" s="19" t="s">
+      <c r="B17" s="6" t="s">
         <v>1030</v>
       </c>
-      <c r="C17" s="19">
+      <c r="C17" s="6">
         <v>-1.0885523235350381</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B18" s="19" t="s">
+      <c r="B18" s="6" t="s">
         <v>1031</v>
       </c>
-      <c r="C18" s="19">
+      <c r="C18" s="6">
         <v>44</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B19" s="19" t="s">
+      <c r="B19" s="6" t="s">
         <v>1032</v>
       </c>
-      <c r="C19" s="19">
+      <c r="C19" s="6">
         <v>55</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B20" s="19" t="s">
+      <c r="B20" s="6" t="s">
         <v>1033</v>
       </c>
-      <c r="C20" s="19">
+      <c r="C20" s="6">
         <v>99</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B21" s="19" t="s">
+      <c r="B21" s="6" t="s">
         <v>1034</v>
       </c>
-      <c r="C21" s="19">
+      <c r="C21" s="6">
         <v>405</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B22" s="19" t="s">
+      <c r="B22" s="6" t="s">
         <v>1035</v>
       </c>
-      <c r="C22" s="19">
+      <c r="C22" s="6">
         <v>5</v>
       </c>
     </row>
@@ -8196,7 +10361,7 @@
       <c r="B2" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="10">
+      <c r="C2" s="6">
         <v>99</v>
       </c>
       <c r="D2" s="6">
@@ -8210,7 +10375,7 @@
       <c r="B3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="10">
+      <c r="C3" s="6">
         <v>86</v>
       </c>
       <c r="D3" s="6">
@@ -8224,7 +10389,7 @@
       <c r="B4" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4" s="6">
         <v>78</v>
       </c>
       <c r="D4" s="6">
@@ -8238,7 +10403,7 @@
       <c r="B5" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="6">
         <v>55</v>
       </c>
       <c r="D5" s="6">
@@ -8252,7 +10417,7 @@
       <c r="B6" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="6">
         <v>87</v>
       </c>
       <c r="D6" s="6">
@@ -8265,100 +10430,100 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B10" s="20"/>
-      <c r="C10" s="20" t="s">
+      <c r="B10" s="13"/>
+      <c r="C10" s="13" t="s">
         <v>1036</v>
       </c>
-      <c r="D10" s="20" t="s">
+      <c r="D10" s="13" t="s">
         <v>1037</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="6" t="s">
         <v>1023</v>
       </c>
-      <c r="C11" s="19">
+      <c r="C11" s="6">
         <v>81</v>
       </c>
-      <c r="D11" s="19">
+      <c r="D11" s="6">
         <v>78.2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="6" t="s">
         <v>1038</v>
       </c>
-      <c r="C12" s="19">
+      <c r="C12" s="6">
         <v>0.5</v>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="6">
         <v>0.5</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="6" t="s">
         <v>1039</v>
       </c>
-      <c r="C13" s="19">
+      <c r="C13" s="6">
         <v>5</v>
       </c>
-      <c r="D13" s="19">
+      <c r="D13" s="6">
         <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="6" t="s">
         <v>1040</v>
       </c>
-      <c r="C14" s="19">
+      <c r="C14" s="6">
         <v>0</v>
       </c>
-      <c r="D14" s="19"/>
+      <c r="D14" s="6"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="6" t="s">
         <v>1041</v>
       </c>
-      <c r="C15" s="19">
+      <c r="C15" s="6">
         <v>6.2609903369994049</v>
       </c>
-      <c r="D15" s="19"/>
+      <c r="D15" s="6"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="6" t="s">
         <v>1042</v>
       </c>
-      <c r="C16" s="19">
+      <c r="C16" s="6">
         <v>1.9127011086084167E-10</v>
       </c>
-      <c r="D16" s="19"/>
+      <c r="D16" s="6"/>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B17" s="19" t="s">
+      <c r="B17" s="6" t="s">
         <v>1043</v>
       </c>
-      <c r="C17" s="19">
+      <c r="C17" s="6">
         <v>1.6448536269514715</v>
       </c>
-      <c r="D17" s="19"/>
+      <c r="D17" s="6"/>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B18" s="19" t="s">
+      <c r="B18" s="6" t="s">
         <v>1044</v>
       </c>
-      <c r="C18" s="19">
+      <c r="C18" s="6">
         <v>3.8254022172168334E-10</v>
       </c>
-      <c r="D18" s="19"/>
+      <c r="D18" s="6"/>
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B19" s="19" t="s">
+      <c r="B19" s="6" t="s">
         <v>1045</v>
       </c>
-      <c r="C19" s="19">
+      <c r="C19" s="6">
         <v>1.9599639845400536</v>
       </c>
-      <c r="D19" s="19"/>
+      <c r="D19" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8396,7 +10561,7 @@
       <c r="B2" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="10">
+      <c r="C2" s="6">
         <v>99</v>
       </c>
       <c r="D2" s="6">
@@ -8410,7 +10575,7 @@
       <c r="B3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="10">
+      <c r="C3" s="6">
         <v>86</v>
       </c>
       <c r="D3" s="6">
@@ -8424,7 +10589,7 @@
       <c r="B4" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4" s="6">
         <v>78</v>
       </c>
       <c r="D4" s="6">
@@ -8438,7 +10603,7 @@
       <c r="B5" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="6">
         <v>55</v>
       </c>
       <c r="D5" s="6">
@@ -8452,7 +10617,7 @@
       <c r="B6" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="6">
         <v>87</v>
       </c>
       <c r="D6" s="6">
@@ -8465,118 +10630,118 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B10" s="20"/>
-      <c r="C10" s="20" t="s">
+      <c r="B10" s="13"/>
+      <c r="C10" s="13" t="s">
         <v>1036</v>
       </c>
-      <c r="D10" s="20" t="s">
+      <c r="D10" s="13" t="s">
         <v>1037</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="6" t="s">
         <v>1023</v>
       </c>
-      <c r="C11" s="19">
+      <c r="C11" s="6">
         <v>81</v>
       </c>
-      <c r="D11" s="19">
+      <c r="D11" s="6">
         <v>78.2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="6" t="s">
         <v>1048</v>
       </c>
-      <c r="C12" s="19">
+      <c r="C12" s="6">
         <v>267.5</v>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="6">
         <v>507.19999999999982</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="6" t="s">
         <v>1039</v>
       </c>
-      <c r="C13" s="19">
+      <c r="C13" s="6">
         <v>5</v>
       </c>
-      <c r="D13" s="19">
+      <c r="D13" s="6">
         <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="6" t="s">
         <v>1049</v>
       </c>
-      <c r="C14" s="19">
+      <c r="C14" s="6">
         <v>0.38008131507270371</v>
       </c>
-      <c r="D14" s="19"/>
+      <c r="D14" s="6"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="6" t="s">
         <v>1040</v>
       </c>
-      <c r="C15" s="19">
+      <c r="C15" s="6">
         <v>0</v>
       </c>
-      <c r="D15" s="19"/>
+      <c r="D15" s="6"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="6" t="s">
         <v>1050</v>
       </c>
-      <c r="C16" s="19">
+      <c r="C16" s="6">
         <v>4</v>
       </c>
-      <c r="D16" s="19"/>
+      <c r="D16" s="6"/>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B17" s="19" t="s">
+      <c r="B17" s="6" t="s">
         <v>1051</v>
       </c>
-      <c r="C17" s="19">
+      <c r="C17" s="6">
         <v>0.28149590298979565</v>
       </c>
-      <c r="D17" s="19"/>
+      <c r="D17" s="6"/>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B18" s="19" t="s">
+      <c r="B18" s="6" t="s">
         <v>1052</v>
       </c>
-      <c r="C18" s="19">
+      <c r="C18" s="6">
         <v>0.39614617646171546</v>
       </c>
-      <c r="D18" s="19"/>
+      <c r="D18" s="6"/>
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B19" s="19" t="s">
+      <c r="B19" s="6" t="s">
         <v>1053</v>
       </c>
-      <c r="C19" s="19">
+      <c r="C19" s="6">
         <v>2.1318467863266499</v>
       </c>
-      <c r="D19" s="19"/>
+      <c r="D19" s="6"/>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B20" s="19" t="s">
+      <c r="B20" s="6" t="s">
         <v>1054</v>
       </c>
-      <c r="C20" s="19">
+      <c r="C20" s="6">
         <v>0.79229235292343092</v>
       </c>
-      <c r="D20" s="19"/>
+      <c r="D20" s="6"/>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B21" s="19" t="s">
+      <c r="B21" s="6" t="s">
         <v>1055</v>
       </c>
-      <c r="C21" s="19">
+      <c r="C21" s="6">
         <v>2.7764451051977934</v>
       </c>
-      <c r="D21" s="19"/>
+      <c r="D21" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8613,7 +10778,7 @@
       <c r="B2" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="10">
+      <c r="C2" s="6">
         <v>99</v>
       </c>
       <c r="D2" s="6">
@@ -8627,7 +10792,7 @@
       <c r="B3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="10">
+      <c r="C3" s="6">
         <v>86</v>
       </c>
       <c r="D3" s="6">
@@ -8641,7 +10806,7 @@
       <c r="B4" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4" s="6">
         <v>78</v>
       </c>
       <c r="D4" s="6">
@@ -8655,7 +10820,7 @@
       <c r="B5" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="6">
         <v>55</v>
       </c>
       <c r="D5" s="6">
@@ -8669,7 +10834,7 @@
       <c r="B6" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="6">
         <v>87</v>
       </c>
       <c r="D6" s="6">
@@ -8688,53 +10853,53 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="20" t="s">
+      <c r="A11" s="13" t="s">
         <v>1058</v>
       </c>
-      <c r="B11" s="20" t="s">
+      <c r="B11" s="13" t="s">
         <v>1035</v>
       </c>
-      <c r="C11" s="20" t="s">
+      <c r="C11" s="13" t="s">
         <v>1034</v>
       </c>
-      <c r="D11" s="20" t="s">
+      <c r="D11" s="13" t="s">
         <v>1059</v>
       </c>
-      <c r="E11" s="20" t="s">
+      <c r="E11" s="13" t="s">
         <v>1048</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="6" t="s">
         <v>1060</v>
       </c>
-      <c r="B12" s="19">
+      <c r="B12" s="6">
         <v>5</v>
       </c>
-      <c r="C12" s="19">
+      <c r="C12" s="6">
         <v>405</v>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="6">
         <v>81</v>
       </c>
-      <c r="E12" s="19">
+      <c r="E12" s="6">
         <v>267.5</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="6" t="s">
         <v>1061</v>
       </c>
-      <c r="B13" s="19">
+      <c r="B13" s="6">
         <v>5</v>
       </c>
-      <c r="C13" s="19">
+      <c r="C13" s="6">
         <v>391</v>
       </c>
-      <c r="D13" s="19">
+      <c r="D13" s="6">
         <v>78.2</v>
       </c>
-      <c r="E13" s="19">
+      <c r="E13" s="6">
         <v>507.19999999999982</v>
       </c>
     </row>
@@ -8744,91 +10909,91 @@
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A17" s="20" t="s">
+      <c r="A17" s="13" t="s">
         <v>1063</v>
       </c>
-      <c r="B17" s="20" t="s">
+      <c r="B17" s="13" t="s">
         <v>1064</v>
       </c>
-      <c r="C17" s="20" t="s">
+      <c r="C17" s="13" t="s">
         <v>1050</v>
       </c>
-      <c r="D17" s="20" t="s">
+      <c r="D17" s="13" t="s">
         <v>1065</v>
       </c>
-      <c r="E17" s="20" t="s">
+      <c r="E17" s="13" t="s">
         <v>1066</v>
       </c>
-      <c r="F17" s="20" t="s">
+      <c r="F17" s="13" t="s">
         <v>1067</v>
       </c>
-      <c r="G17" s="20" t="s">
+      <c r="G17" s="13" t="s">
         <v>1068</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A18" s="19" t="s">
+      <c r="A18" s="6" t="s">
         <v>1069</v>
       </c>
-      <c r="B18" s="19">
+      <c r="B18" s="6">
         <v>19.600000000000364</v>
       </c>
-      <c r="C18" s="19">
+      <c r="C18" s="6">
         <v>1</v>
       </c>
-      <c r="D18" s="19">
+      <c r="D18" s="6">
         <v>19.600000000000364</v>
       </c>
-      <c r="E18" s="19">
+      <c r="E18" s="6">
         <v>5.0600232348006625E-2</v>
       </c>
-      <c r="F18" s="19">
+      <c r="F18" s="6">
         <v>0.82766152108105717</v>
       </c>
-      <c r="G18" s="19">
+      <c r="G18" s="6">
         <v>5.3176550715787174</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A19" s="19" t="s">
+      <c r="A19" s="6" t="s">
         <v>1070</v>
       </c>
-      <c r="B19" s="19">
+      <c r="B19" s="6">
         <v>3098.7999999999997</v>
       </c>
-      <c r="C19" s="19">
+      <c r="C19" s="6">
         <v>8</v>
       </c>
-      <c r="D19" s="19">
+      <c r="D19" s="6">
         <v>387.34999999999997</v>
       </c>
-      <c r="E19" s="19"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="19"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A20" s="19"/>
-      <c r="B20" s="19"/>
-      <c r="C20" s="19"/>
-      <c r="D20" s="19"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="19"/>
-      <c r="G20" s="19"/>
+      <c r="A20" s="6"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A21" s="19" t="s">
+      <c r="A21" s="6" t="s">
         <v>1071</v>
       </c>
-      <c r="B21" s="19">
+      <c r="B21" s="6">
         <v>3118.4</v>
       </c>
-      <c r="C21" s="19">
+      <c r="C21" s="6">
         <v>9</v>
       </c>
-      <c r="D21" s="19"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="19"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8861,7 +11026,7 @@
       <c r="B2" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="10">
+      <c r="C2" s="6">
         <v>99</v>
       </c>
       <c r="D2" s="6">
@@ -8875,7 +11040,7 @@
       <c r="B3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="10">
+      <c r="C3" s="6">
         <v>86</v>
       </c>
       <c r="D3" s="6">
@@ -8889,7 +11054,7 @@
       <c r="B4" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="10"/>
+      <c r="C4" s="6"/>
       <c r="D4" s="6">
         <v>89</v>
       </c>
@@ -8901,7 +11066,7 @@
       <c r="B5" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="6">
         <v>55</v>
       </c>
       <c r="D5" s="6">
@@ -8915,7 +11080,7 @@
       <c r="B6" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="6">
         <v>87</v>
       </c>
       <c r="D6" s="6">
@@ -8924,6 +11089,72 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3D1F3AA-B5A5-493D-9289-258E322BAB25}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="6" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B2" s="6">
+        <v>89</v>
+      </c>
+      <c r="C2" s="6">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="6" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B3" s="6">
+        <v>42</v>
+      </c>
+      <c r="C3" s="6">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="6">
+        <v>99</v>
+      </c>
+      <c r="C4" s="6">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="6">
+        <v>87</v>
+      </c>
+      <c r="C5" s="6">
+        <v>90</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
